--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1. Лист «Команда»: впишите участников и их роли.</t>
+          <t>1. Лист «Команда»: впишите участников и их роли. В списке — четыре роли с первого занятия; если команда придумала свои роли, впишите их вручную.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Роль в команде</t>
+          <t>Роль в команде: из списка или своя</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -865,7 +865,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"лидер,аналитик,технический эксперт,коммуникатор"</formula1>
     </dataValidation>
   </dataValidations>

--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -1052,7 +1052,7 @@
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(H7="дней",1/7,1),0)</f>
+        <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(H8="дней",1/7,1),0)</f>
+        <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(H9="дней",1/7,1),0)</f>
+        <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(H10="дней",1/7,1),0)</f>
+        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(H11="дней",1/7,1),0)</f>
+        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(H12="дней",1/7,1),0)</f>
+        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(H13="дней",1/7,1),0)</f>
+        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(H14="дней",1/7,1),0)</f>
+        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(H15="дней",1/7,1),0)</f>
+        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(H16="дней",1/7,1),0)</f>
+        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(H17="дней",1/7,1),0)</f>
+        <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(H18="дней",1/7,1),0)</f>
+        <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(H19="дней",1/7,1),0)</f>
+        <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(H20="дней",1/7,1),0)</f>
+        <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(H21="дней",1/7,1),0)</f>
+        <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(H22="дней",1/7,1),0)</f>
+        <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(H23="дней",1/7,1),0)</f>
+        <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(H24="дней",1/7,1),0)</f>
+        <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(H25="дней",1/7,1),0)</f>
+        <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(H26="дней",1/7,1),0)</f>
+        <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(H27="дней",1/7,1),0)</f>
+        <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(H28="дней",1/7,1),0)</f>
+        <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(H29="дней",1/7,1),0)</f>
+        <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(H30="дней",1/7,1),0)</f>
+        <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(H31="дней",1/7,1),0)</f>
+        <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(H32="дней",1/7,1),0)</f>
+        <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(H33="дней",1/7,1),0)</f>
+        <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(H34="дней",1/7,1),0)</f>
+        <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(H35="дней",1/7,1),0)</f>
+        <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(H36="дней",1/7,1),0)</f>
+        <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(H37="дней",1/7,1),0)</f>
+        <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(H38="дней",1/7,1),0)</f>
+        <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(H39="дней",1/7,1),0)</f>
+        <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v/>
       </c>
       <c r="K40" s="16">
-        <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(H40="дней",1/7,1),0)</f>
+        <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
         <v/>
       </c>
       <c r="K41" s="16">
-        <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(H41="дней",1/7,1),0)</f>
+        <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v/>
       </c>
       <c r="K42" s="16">
-        <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(H42="дней",1/7,1),0)</f>
+        <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
         <v/>
       </c>
       <c r="K43" s="16">
-        <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(H43="дней",1/7,1),0)</f>
+        <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="K44" s="16">
-        <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(H44="дней",1/7,1),0)</f>
+        <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="K45" s="16">
-        <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(H45="дней",1/7,1),0)</f>
+        <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <v/>
       </c>
       <c r="K46" s="16">
-        <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(H46="дней",1/7,1),0)</f>
+        <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         <v/>
       </c>
       <c r="K47" s="16">
-        <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(H47="дней",1/7,1),0)</f>
+        <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         <v/>
       </c>
       <c r="K48" s="16">
-        <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(H48="дней",1/7,1),0)</f>
+        <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         <v/>
       </c>
       <c r="K49" s="16">
-        <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(H49="дней",1/7,1),0)</f>
+        <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v/>
       </c>
       <c r="K50" s="16">
-        <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(H50="дней",1/7,1),0)</f>
+        <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v/>
       </c>
       <c r="K51" s="16">
-        <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(H51="дней",1/7,1),0)</f>
+        <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         <v/>
       </c>
       <c r="K52" s="16">
-        <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(H52="дней",1/7,1),0)</f>
+        <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v/>
       </c>
       <c r="K53" s="16">
-        <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(H53="дней",1/7,1),0)</f>
+        <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
         <v/>
       </c>
       <c r="K54" s="16">
-        <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(H54="дней",1/7,1),0)</f>
+        <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
         <v/>
       </c>
       <c r="K55" s="16">
-        <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(H55="дней",1/7,1),0)</f>
+        <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
         <v/>
       </c>
       <c r="K56" s="16">
-        <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(H56="дней",1/7,1),0)</f>
+        <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
         <v/>
       </c>
       <c r="K57" s="16">
-        <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(H57="дней",1/7,1),0)</f>
+        <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v/>
       </c>
       <c r="K58" s="16">
-        <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(H58="дней",1/7,1),0)</f>
+        <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
         <v/>
       </c>
       <c r="K59" s="16">
-        <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(H59="дней",1/7,1),0)</f>
+        <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
         <v/>
       </c>
       <c r="K60" s="16">
-        <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(H60="дней",1/7,1),0)</f>
+        <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="K61" s="16">
-        <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(H61="дней",1/7,1),0)</f>
+        <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="K62" s="16">
-        <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(H62="дней",1/7,1),0)</f>
+        <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
         <v/>
       </c>
       <c r="K63" s="16">
-        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(H63="дней",1/7,1),0)</f>
+        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
         <v/>
       </c>
       <c r="K64" s="16">
-        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(H64="дней",1/7,1),0)</f>
+        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
         <v/>
       </c>
       <c r="K65" s="16">
-        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(H65="дней",1/7,1),0)</f>
+        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v/>
       </c>
       <c r="K66" s="16">
-        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(H66="дней",1/7,1),0)</f>
+        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2569,10 +2569,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
       <formula1>"недель,дней"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ответственный" error="Этого человека нет на листе «Команда». Ответственный — один человек." type="list" errorStyle="warning">
+    <dataValidation sqref="F7:F66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ответственный" error="Этого человека нет на листе «Команда». Ответственный — один человек." type="list" errorStyle="warning">
       <formula1>Команда!$A$5:$A$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -2773,7 +2773,7 @@
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(H7="дней",1/7,1),0)</f>
+        <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(H8="дней",1/7,1),0)</f>
+        <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(H9="дней",1/7,1),0)</f>
+        <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(H10="дней",1/7,1),0)</f>
+        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(H11="дней",1/7,1),0)</f>
+        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(H12="дней",1/7,1),0)</f>
+        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(H13="дней",1/7,1),0)</f>
+        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(H14="дней",1/7,1),0)</f>
+        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(H15="дней",1/7,1),0)</f>
+        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(H16="дней",1/7,1),0)</f>
+        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(H17="дней",1/7,1),0)</f>
+        <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(H18="дней",1/7,1),0)</f>
+        <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(H19="дней",1/7,1),0)</f>
+        <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(H20="дней",1/7,1),0)</f>
+        <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(H21="дней",1/7,1),0)</f>
+        <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(H22="дней",1/7,1),0)</f>
+        <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(H23="дней",1/7,1),0)</f>
+        <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(H24="дней",1/7,1),0)</f>
+        <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(H25="дней",1/7,1),0)</f>
+        <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(H26="дней",1/7,1),0)</f>
+        <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(H27="дней",1/7,1),0)</f>
+        <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(H28="дней",1/7,1),0)</f>
+        <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(H29="дней",1/7,1),0)</f>
+        <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(H30="дней",1/7,1),0)</f>
+        <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(H31="дней",1/7,1),0)</f>
+        <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(H32="дней",1/7,1),0)</f>
+        <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(H33="дней",1/7,1),0)</f>
+        <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(H34="дней",1/7,1),0)</f>
+        <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(H35="дней",1/7,1),0)</f>
+        <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(H36="дней",1/7,1),0)</f>
+        <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(H37="дней",1/7,1),0)</f>
+        <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(H38="дней",1/7,1),0)</f>
+        <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(H39="дней",1/7,1),0)</f>
+        <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
         <v/>
       </c>
       <c r="K40" s="16">
-        <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(H40="дней",1/7,1),0)</f>
+        <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v/>
       </c>
       <c r="K41" s="16">
-        <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(H41="дней",1/7,1),0)</f>
+        <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="K42" s="16">
-        <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(H42="дней",1/7,1),0)</f>
+        <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v/>
       </c>
       <c r="K43" s="16">
-        <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(H43="дней",1/7,1),0)</f>
+        <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
         <v/>
       </c>
       <c r="K44" s="16">
-        <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(H44="дней",1/7,1),0)</f>
+        <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
         <v/>
       </c>
       <c r="K45" s="16">
-        <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(H45="дней",1/7,1),0)</f>
+        <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
         <v/>
       </c>
       <c r="K46" s="16">
-        <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(H46="дней",1/7,1),0)</f>
+        <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="K47" s="16">
-        <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(H47="дней",1/7,1),0)</f>
+        <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="K48" s="16">
-        <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(H48="дней",1/7,1),0)</f>
+        <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v/>
       </c>
       <c r="K49" s="16">
-        <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(H49="дней",1/7,1),0)</f>
+        <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
         <v/>
       </c>
       <c r="K50" s="16">
-        <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(H50="дней",1/7,1),0)</f>
+        <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
         <v/>
       </c>
       <c r="K51" s="16">
-        <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(H51="дней",1/7,1),0)</f>
+        <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
         <v/>
       </c>
       <c r="K52" s="16">
-        <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(H52="дней",1/7,1),0)</f>
+        <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
         <v/>
       </c>
       <c r="K53" s="16">
-        <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(H53="дней",1/7,1),0)</f>
+        <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="K54" s="16">
-        <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(H54="дней",1/7,1),0)</f>
+        <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
         <v/>
       </c>
       <c r="K55" s="16">
-        <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(H55="дней",1/7,1),0)</f>
+        <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="K56" s="16">
-        <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(H56="дней",1/7,1),0)</f>
+        <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v/>
       </c>
       <c r="K57" s="16">
-        <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(H57="дней",1/7,1),0)</f>
+        <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="K58" s="16">
-        <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(H58="дней",1/7,1),0)</f>
+        <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="K59" s="16">
-        <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(H59="дней",1/7,1),0)</f>
+        <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
         <v/>
       </c>
       <c r="K60" s="16">
-        <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(H60="дней",1/7,1),0)</f>
+        <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
         <v/>
       </c>
       <c r="K61" s="16">
-        <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(H61="дней",1/7,1),0)</f>
+        <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
         <v/>
       </c>
       <c r="K62" s="16">
-        <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(H62="дней",1/7,1),0)</f>
+        <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         <v/>
       </c>
       <c r="K63" s="16">
-        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(H63="дней",1/7,1),0)</f>
+        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
         <v/>
       </c>
       <c r="K64" s="16">
-        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(H64="дней",1/7,1),0)</f>
+        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         <v/>
       </c>
       <c r="K65" s="16">
-        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(H65="дней",1/7,1),0)</f>
+        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
         <v/>
       </c>
       <c r="K66" s="16">
-        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(H66="дней",1/7,1),0)</f>
+        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
       <formula1>"недель,дней"</formula1>
     </dataValidation>
   </dataValidations>

--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -36,57 +36,57 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00005AAA"/>
+      <color rgb="FF005AAA"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00002C5F"/>
+      <color rgb="FF002C5F"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00005AAA"/>
+      <color rgb="FF005AAA"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00005AAA"/>
+      <color rgb="FF005AAA"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="007F8C9A"/>
+      <color rgb="FF7F8C9A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00002C5F"/>
+      <color rgb="FF002C5F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00002C5F"/>
+      <color rgb="FF002C5F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00002C5F"/>
+      <color rgb="FF002C5F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="007F8C9A"/>
+      <color rgb="FF7F8C9A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="007F8C9A"/>
+      <color rgb="FF7F8C9A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -99,14 +99,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E6F3"/>
-        <bgColor rgb="00D9E6F3"/>
+        <fgColor rgb="FFD9E6F3"/>
+        <bgColor rgb="FFD9E6F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F8"/>
-        <bgColor rgb="00F4F6F8"/>
+        <fgColor rgb="FFF4F6F8"/>
+        <bgColor rgb="FFF4F6F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,21 +120,21 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B3B3B3"/>
+        <color rgb="FFB3B3B3"/>
       </left>
       <right style="thin">
-        <color rgb="00B3B3B3"/>
+        <color rgb="FFB3B3B3"/>
       </right>
       <top style="thin">
-        <color rgb="00B3B3B3"/>
+        <color rgb="FFB3B3B3"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B3B3B3"/>
+        <color rgb="FFB3B3B3"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00002C5F"/>
+        <color rgb="FF002C5F"/>
       </bottom>
     </border>
   </borders>
@@ -193,25 +193,25 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00002C5F"/>
+        <color rgb="FF002C5F"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E6EFF8"/>
-          <bgColor rgb="00E6EFF8"/>
+          <fgColor rgb="FFE6EFF8"/>
+          <bgColor rgb="FFE6EFF8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00E70F47"/>
+        <color rgb="FFE70F47"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00009A49"/>
+        <color rgb="FF009A49"/>
       </font>
     </dxf>
   </dxfs>
@@ -876,7 +876,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00005AAA"/>
+    <tabColor rgb="FF005AAA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2585,7 +2585,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F8C9A"/>
+    <tabColor rgb="FF7F8C9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -90,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +101,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E6F3"/>
         <bgColor rgb="FFD9E6F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E1"/>
+        <bgColor rgb="FFFFF9E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -165,6 +171,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,7 +188,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +616,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1. Лист «Команда»: впишите участников и их роли. В списке — четыре роли с первого занятия; если команда придумала свои роли, впишите их вручную.</t>
+          <t>1. Лист «Команда»: впишите участников и выберите роли. В списке «Роли команды» справа — четыре роли с первого занятия; если команда придумала свои роли, впишите их в пустые строки этого списка — они появятся в выпадающем меню.</t>
         </is>
       </c>
     </row>
@@ -735,13 +744,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -766,7 +777,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Роль в команде: из списка или своя</t>
+          <t>Роль в команде (список справа)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -777,6 +788,11 @@
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Недель работы</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Роли команды (список)</t>
         </is>
       </c>
     </row>
@@ -791,6 +807,11 @@
         <f>IF(A5="","",ROUND(SUMIF(WBS!$F$7:$F$66,A5,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>лидер</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -803,6 +824,11 @@
         <f>IF(A6="","",ROUND(SUMIF(WBS!$F$7:$F$66,A6,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>аналитик</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -815,6 +841,11 @@
         <f>IF(A7="","",ROUND(SUMIF(WBS!$F$7:$F$66,A7,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>технический эксперт</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -827,6 +858,11 @@
         <f>IF(A8="","",ROUND(SUMIF(WBS!$F$7:$F$66,A8,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>коммуникатор</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -839,6 +875,7 @@
         <f>IF(A9="","",ROUND(SUMIF(WBS!$F$7:$F$66,A9,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -851,11 +888,23 @@
         <f>IF(A10="","",ROUND(SUMIF(WBS!$F$7:$F$66,A10,WBS!$K$7:$K$66),1))</f>
         <v/>
       </c>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Если у одного человека намного больше недель, чем у других, перераспределите пакеты сейчас, до диаграммы Ганта.</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Свою роль впишите в пустую строку выше — она появится в выпадающем списке «Роль».</t>
         </is>
       </c>
     </row>
@@ -866,7 +915,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5 B6 B7 B8 B9 B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"лидер,аналитик,технический эксперт,коммуникатор"</formula1>
+      <formula1>$F$5:$F$12</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -904,40 +953,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Проект:</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
+      <c r="B2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Результатов</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Пакетов работ</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Замечаний</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>«Отчёт и защита»</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>«Управление проектом»</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Сумма, недель</t>
         </is>
@@ -949,27 +998,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <f>COUNTIFS($B$7:$B$66,1)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="13">
         <f>COUNTIF($D$7:$D$66,"пакет работ")</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <f>COUNTIF($J$7:$J$66,"?*")-COUNTIF($J$7:$J$66,"✓")</f>
         <v/>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*отч*")&gt;0,"✓ есть","добавьте")</f>
         <v/>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*управл*")&gt;0,"✓ есть","добавьте")</f>
         <v/>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <f>ROUND(SUM($K$7:$K$66),1)</f>
         <v/>
       </c>
@@ -1032,13 +1081,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
-      <c r="B7" s="14">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="15">
         <f>IF(A7="","",LEN(A7)-LEN(SUBSTITUTE(A7,".",""))+1)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$7:$A$66,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1046,24 +1095,24 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
-      <c r="I7" s="15" t="n"/>
+      <c r="I7" s="16" t="n"/>
       <c r="J7" s="7">
         <f>IF(A7="","",IF(COUNTIF($A$7:$A$66,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$7:$A$66,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="17">
         <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="14">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15">
         <f>IF(A8="","",LEN(A8)-LEN(SUBSTITUTE(A8,".",""))+1)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$7:$A$66,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1071,24 +1120,24 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="15" t="n"/>
+      <c r="I8" s="16" t="n"/>
       <c r="J8" s="7">
         <f>IF(A8="","",IF(COUNTIF($A$7:$A$66,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$7:$A$66,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="17">
         <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="14">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15">
         <f>IF(A9="","",LEN(A9)-LEN(SUBSTITUTE(A9,".",""))+1)</f>
         <v/>
       </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$7:$A$66,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1096,24 +1145,24 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
-      <c r="I9" s="15" t="n"/>
+      <c r="I9" s="16" t="n"/>
       <c r="J9" s="7">
         <f>IF(A9="","",IF(COUNTIF($A$7:$A$66,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$7:$A$66,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="17">
         <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="14">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="15">
         <f>IF(A10="","",LEN(A10)-LEN(SUBSTITUTE(A10,".",""))+1)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$7:$A$66,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1121,24 +1170,24 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="15" t="n"/>
+      <c r="I10" s="16" t="n"/>
       <c r="J10" s="7">
         <f>IF(A10="","",IF(COUNTIF($A$7:$A$66,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$7:$A$66,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="17">
         <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="14">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15">
         <f>IF(A11="","",LEN(A11)-LEN(SUBSTITUTE(A11,".",""))+1)</f>
         <v/>
       </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$7:$A$66,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1146,24 +1195,24 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
-      <c r="I11" s="15" t="n"/>
+      <c r="I11" s="16" t="n"/>
       <c r="J11" s="7">
         <f>IF(A11="","",IF(COUNTIF($A$7:$A$66,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$7:$A$66,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="17">
         <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n"/>
-      <c r="B12" s="14">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="15">
         <f>IF(A12="","",LEN(A12)-LEN(SUBSTITUTE(A12,".",""))+1)</f>
         <v/>
       </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$7:$A$66,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1171,24 +1220,24 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
-      <c r="I12" s="15" t="n"/>
+      <c r="I12" s="16" t="n"/>
       <c r="J12" s="7">
         <f>IF(A12="","",IF(COUNTIF($A$7:$A$66,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$7:$A$66,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="17">
         <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="14">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="15">
         <f>IF(A13="","",LEN(A13)-LEN(SUBSTITUTE(A13,".",""))+1)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$7:$A$66,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1196,24 +1245,24 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
-      <c r="I13" s="15" t="n"/>
+      <c r="I13" s="16" t="n"/>
       <c r="J13" s="7">
         <f>IF(A13="","",IF(COUNTIF($A$7:$A$66,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$7:$A$66,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="17">
         <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n"/>
-      <c r="B14" s="14">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="15">
         <f>IF(A14="","",LEN(A14)-LEN(SUBSTITUTE(A14,".",""))+1)</f>
         <v/>
       </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$7:$A$66,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1221,24 +1270,24 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="16" t="n"/>
       <c r="J14" s="7">
         <f>IF(A14="","",IF(COUNTIF($A$7:$A$66,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$7:$A$66,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="17">
         <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="14">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="15">
         <f>IF(A15="","",LEN(A15)-LEN(SUBSTITUTE(A15,".",""))+1)</f>
         <v/>
       </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="14">
+      <c r="D15" s="15">
         <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$7:$A$66,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1246,24 +1295,24 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
-      <c r="I15" s="15" t="n"/>
+      <c r="I15" s="16" t="n"/>
       <c r="J15" s="7">
         <f>IF(A15="","",IF(COUNTIF($A$7:$A$66,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$7:$A$66,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="17">
         <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n"/>
-      <c r="B16" s="14">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15">
         <f>IF(A16="","",LEN(A16)-LEN(SUBSTITUTE(A16,".",""))+1)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$7:$A$66,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1271,24 +1320,24 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
-      <c r="I16" s="15" t="n"/>
+      <c r="I16" s="16" t="n"/>
       <c r="J16" s="7">
         <f>IF(A16="","",IF(COUNTIF($A$7:$A$66,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$7:$A$66,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="17">
         <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="14">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="15">
         <f>IF(A17="","",LEN(A17)-LEN(SUBSTITUTE(A17,".",""))+1)</f>
         <v/>
       </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$7:$A$66,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1296,24 +1345,24 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
-      <c r="I17" s="15" t="n"/>
+      <c r="I17" s="16" t="n"/>
       <c r="J17" s="7">
         <f>IF(A17="","",IF(COUNTIF($A$7:$A$66,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$7:$A$66,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="17">
         <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n"/>
-      <c r="B18" s="14">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="15">
         <f>IF(A18="","",LEN(A18)-LEN(SUBSTITUTE(A18,".",""))+1)</f>
         <v/>
       </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$7:$A$66,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1321,24 +1370,24 @@
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
-      <c r="I18" s="15" t="n"/>
+      <c r="I18" s="16" t="n"/>
       <c r="J18" s="7">
         <f>IF(A18="","",IF(COUNTIF($A$7:$A$66,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$7:$A$66,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="17">
         <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="14">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="15">
         <f>IF(A19="","",LEN(A19)-LEN(SUBSTITUTE(A19,".",""))+1)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$7:$A$66,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1346,24 +1395,24 @@
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
-      <c r="I19" s="15" t="n"/>
+      <c r="I19" s="16" t="n"/>
       <c r="J19" s="7">
         <f>IF(A19="","",IF(COUNTIF($A$7:$A$66,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$7:$A$66,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="17">
         <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n"/>
-      <c r="B20" s="14">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="15">
         <f>IF(A20="","",LEN(A20)-LEN(SUBSTITUTE(A20,".",""))+1)</f>
         <v/>
       </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$7:$A$66,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1371,24 +1420,24 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="15" t="n"/>
+      <c r="I20" s="16" t="n"/>
       <c r="J20" s="7">
         <f>IF(A20="","",IF(COUNTIF($A$7:$A$66,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$7:$A$66,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="17">
         <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n"/>
-      <c r="B21" s="14">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15">
         <f>IF(A21="","",LEN(A21)-LEN(SUBSTITUTE(A21,".",""))+1)</f>
         <v/>
       </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$7:$A$66,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1396,24 +1445,24 @@
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
-      <c r="I21" s="15" t="n"/>
+      <c r="I21" s="16" t="n"/>
       <c r="J21" s="7">
         <f>IF(A21="","",IF(COUNTIF($A$7:$A$66,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$7:$A$66,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="17">
         <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="14">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15">
         <f>IF(A22="","",LEN(A22)-LEN(SUBSTITUTE(A22,".",""))+1)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$7:$A$66,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1421,24 +1470,24 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="15" t="n"/>
+      <c r="I22" s="16" t="n"/>
       <c r="J22" s="7">
         <f>IF(A22="","",IF(COUNTIF($A$7:$A$66,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$7:$A$66,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="17">
         <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="14">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15">
         <f>IF(A23="","",LEN(A23)-LEN(SUBSTITUTE(A23,".",""))+1)</f>
         <v/>
       </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$7:$A$66,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1446,24 +1495,24 @@
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
-      <c r="I23" s="15" t="n"/>
+      <c r="I23" s="16" t="n"/>
       <c r="J23" s="7">
         <f>IF(A23="","",IF(COUNTIF($A$7:$A$66,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$7:$A$66,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="17">
         <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="14">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15">
         <f>IF(A24="","",LEN(A24)-LEN(SUBSTITUTE(A24,".",""))+1)</f>
         <v/>
       </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$7:$A$66,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1471,24 +1520,24 @@
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
-      <c r="I24" s="15" t="n"/>
+      <c r="I24" s="16" t="n"/>
       <c r="J24" s="7">
         <f>IF(A24="","",IF(COUNTIF($A$7:$A$66,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$7:$A$66,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="17">
         <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n"/>
-      <c r="B25" s="14">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15">
         <f>IF(A25="","",LEN(A25)-LEN(SUBSTITUTE(A25,".",""))+1)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$7:$A$66,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1496,24 +1545,24 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
-      <c r="I25" s="15" t="n"/>
+      <c r="I25" s="16" t="n"/>
       <c r="J25" s="7">
         <f>IF(A25="","",IF(COUNTIF($A$7:$A$66,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$7:$A$66,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="17">
         <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="n"/>
-      <c r="B26" s="14">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15">
         <f>IF(A26="","",LEN(A26)-LEN(SUBSTITUTE(A26,".",""))+1)</f>
         <v/>
       </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$7:$A$66,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1521,24 +1570,24 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
-      <c r="I26" s="15" t="n"/>
+      <c r="I26" s="16" t="n"/>
       <c r="J26" s="7">
         <f>IF(A26="","",IF(COUNTIF($A$7:$A$66,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$7:$A$66,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="17">
         <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n"/>
-      <c r="B27" s="14">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15">
         <f>IF(A27="","",LEN(A27)-LEN(SUBSTITUTE(A27,".",""))+1)</f>
         <v/>
       </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$7:$A$66,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1546,24 +1595,24 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="15" t="n"/>
+      <c r="I27" s="16" t="n"/>
       <c r="J27" s="7">
         <f>IF(A27="","",IF(COUNTIF($A$7:$A$66,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$7:$A$66,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="17">
         <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n"/>
-      <c r="B28" s="14">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15">
         <f>IF(A28="","",LEN(A28)-LEN(SUBSTITUTE(A28,".",""))+1)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$7:$A$66,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1571,24 +1620,24 @@
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="15" t="n"/>
+      <c r="I28" s="16" t="n"/>
       <c r="J28" s="7">
         <f>IF(A28="","",IF(COUNTIF($A$7:$A$66,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$7:$A$66,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="17">
         <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n"/>
-      <c r="B29" s="14">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15">
         <f>IF(A29="","",LEN(A29)-LEN(SUBSTITUTE(A29,".",""))+1)</f>
         <v/>
       </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$7:$A$66,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1596,24 +1645,24 @@
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="15" t="n"/>
+      <c r="I29" s="16" t="n"/>
       <c r="J29" s="7">
         <f>IF(A29="","",IF(COUNTIF($A$7:$A$66,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$7:$A$66,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="17">
         <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n"/>
-      <c r="B30" s="14">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15">
         <f>IF(A30="","",LEN(A30)-LEN(SUBSTITUTE(A30,".",""))+1)</f>
         <v/>
       </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$7:$A$66,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1621,24 +1670,24 @@
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="15" t="n"/>
+      <c r="I30" s="16" t="n"/>
       <c r="J30" s="7">
         <f>IF(A30="","",IF(COUNTIF($A$7:$A$66,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$7:$A$66,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="17">
         <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="14">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15">
         <f>IF(A31="","",LEN(A31)-LEN(SUBSTITUTE(A31,".",""))+1)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="14">
+      <c r="D31" s="15">
         <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$7:$A$66,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1646,24 +1695,24 @@
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="15" t="n"/>
+      <c r="I31" s="16" t="n"/>
       <c r="J31" s="7">
         <f>IF(A31="","",IF(COUNTIF($A$7:$A$66,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$7:$A$66,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="17">
         <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n"/>
-      <c r="B32" s="14">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15">
         <f>IF(A32="","",LEN(A32)-LEN(SUBSTITUTE(A32,".",""))+1)</f>
         <v/>
       </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$7:$A$66,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1671,24 +1720,24 @@
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="15" t="n"/>
+      <c r="I32" s="16" t="n"/>
       <c r="J32" s="7">
         <f>IF(A32="","",IF(COUNTIF($A$7:$A$66,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$7:$A$66,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="17">
         <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="14">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15">
         <f>IF(A33="","",LEN(A33)-LEN(SUBSTITUTE(A33,".",""))+1)</f>
         <v/>
       </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="14">
+      <c r="D33" s="15">
         <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$7:$A$66,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1696,24 +1745,24 @@
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="15" t="n"/>
+      <c r="I33" s="16" t="n"/>
       <c r="J33" s="7">
         <f>IF(A33="","",IF(COUNTIF($A$7:$A$66,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$7:$A$66,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="17">
         <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n"/>
-      <c r="B34" s="14">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15">
         <f>IF(A34="","",LEN(A34)-LEN(SUBSTITUTE(A34,".",""))+1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$7:$A$66,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1721,24 +1770,24 @@
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="15" t="n"/>
+      <c r="I34" s="16" t="n"/>
       <c r="J34" s="7">
         <f>IF(A34="","",IF(COUNTIF($A$7:$A$66,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$7:$A$66,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="17">
         <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="14">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15">
         <f>IF(A35="","",LEN(A35)-LEN(SUBSTITUTE(A35,".",""))+1)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$7:$A$66,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1746,24 +1795,24 @@
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="15" t="n"/>
+      <c r="I35" s="16" t="n"/>
       <c r="J35" s="7">
         <f>IF(A35="","",IF(COUNTIF($A$7:$A$66,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$7:$A$66,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="17">
         <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n"/>
-      <c r="B36" s="14">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="15">
         <f>IF(A36="","",LEN(A36)-LEN(SUBSTITUTE(A36,".",""))+1)</f>
         <v/>
       </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$7:$A$66,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1771,24 +1820,24 @@
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="15" t="n"/>
+      <c r="I36" s="16" t="n"/>
       <c r="J36" s="7">
         <f>IF(A36="","",IF(COUNTIF($A$7:$A$66,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$7:$A$66,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="17">
         <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
-      <c r="B37" s="14">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="15">
         <f>IF(A37="","",LEN(A37)-LEN(SUBSTITUTE(A37,".",""))+1)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$7:$A$66,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1796,24 +1845,24 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="15" t="n"/>
+      <c r="I37" s="16" t="n"/>
       <c r="J37" s="7">
         <f>IF(A37="","",IF(COUNTIF($A$7:$A$66,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$7:$A$66,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="17">
         <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n"/>
-      <c r="B38" s="14">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15">
         <f>IF(A38="","",LEN(A38)-LEN(SUBSTITUTE(A38,".",""))+1)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$7:$A$66,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1821,24 +1870,24 @@
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
-      <c r="I38" s="15" t="n"/>
+      <c r="I38" s="16" t="n"/>
       <c r="J38" s="7">
         <f>IF(A38="","",IF(COUNTIF($A$7:$A$66,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$7:$A$66,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="17">
         <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="14">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15">
         <f>IF(A39="","",LEN(A39)-LEN(SUBSTITUTE(A39,".",""))+1)</f>
         <v/>
       </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="14">
+      <c r="D39" s="15">
         <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$7:$A$66,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1846,24 +1895,24 @@
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="15" t="n"/>
+      <c r="I39" s="16" t="n"/>
       <c r="J39" s="7">
         <f>IF(A39="","",IF(COUNTIF($A$7:$A$66,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$7:$A$66,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="17">
         <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="14">
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="15">
         <f>IF(A40="","",LEN(A40)-LEN(SUBSTITUTE(A40,".",""))+1)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$7:$A$66,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1871,24 +1920,24 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="15" t="n"/>
+      <c r="I40" s="16" t="n"/>
       <c r="J40" s="7">
         <f>IF(A40="","",IF(COUNTIF($A$7:$A$66,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$7:$A$66,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="17">
         <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n"/>
-      <c r="B41" s="14">
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="15">
         <f>IF(A41="","",LEN(A41)-LEN(SUBSTITUTE(A41,".",""))+1)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="14">
+      <c r="D41" s="15">
         <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$7:$A$66,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1896,24 +1945,24 @@
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="15" t="n"/>
+      <c r="I41" s="16" t="n"/>
       <c r="J41" s="7">
         <f>IF(A41="","",IF(COUNTIF($A$7:$A$66,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$7:$A$66,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="17">
         <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n"/>
-      <c r="B42" s="14">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15">
         <f>IF(A42="","",LEN(A42)-LEN(SUBSTITUTE(A42,".",""))+1)</f>
         <v/>
       </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$7:$A$66,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1921,24 +1970,24 @@
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
-      <c r="I42" s="15" t="n"/>
+      <c r="I42" s="16" t="n"/>
       <c r="J42" s="7">
         <f>IF(A42="","",IF(COUNTIF($A$7:$A$66,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$7:$A$66,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="17">
         <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n"/>
-      <c r="B43" s="14">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15">
         <f>IF(A43="","",LEN(A43)-LEN(SUBSTITUTE(A43,".",""))+1)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="14">
+      <c r="D43" s="15">
         <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$7:$A$66,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1946,24 +1995,24 @@
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
-      <c r="I43" s="15" t="n"/>
+      <c r="I43" s="16" t="n"/>
       <c r="J43" s="7">
         <f>IF(A43="","",IF(COUNTIF($A$7:$A$66,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$7:$A$66,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="17">
         <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="n"/>
-      <c r="B44" s="14">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15">
         <f>IF(A44="","",LEN(A44)-LEN(SUBSTITUTE(A44,".",""))+1)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$7:$A$66,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1971,24 +2020,24 @@
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="15" t="n"/>
+      <c r="I44" s="16" t="n"/>
       <c r="J44" s="7">
         <f>IF(A44="","",IF(COUNTIF($A$7:$A$66,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$7:$A$66,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="17">
         <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="n"/>
-      <c r="B45" s="14">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="15">
         <f>IF(A45="","",LEN(A45)-LEN(SUBSTITUTE(A45,".",""))+1)</f>
         <v/>
       </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="14">
+      <c r="D45" s="15">
         <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$7:$A$66,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -1996,24 +2045,24 @@
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="15" t="n"/>
+      <c r="I45" s="16" t="n"/>
       <c r="J45" s="7">
         <f>IF(A45="","",IF(COUNTIF($A$7:$A$66,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$7:$A$66,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="17">
         <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n"/>
-      <c r="B46" s="14">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="15">
         <f>IF(A46="","",LEN(A46)-LEN(SUBSTITUTE(A46,".",""))+1)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$7:$A$66,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2021,24 +2070,24 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="15" t="n"/>
+      <c r="I46" s="16" t="n"/>
       <c r="J46" s="7">
         <f>IF(A46="","",IF(COUNTIF($A$7:$A$66,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$7:$A$66,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="17">
         <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n"/>
-      <c r="B47" s="14">
+      <c r="A47" s="14" t="n"/>
+      <c r="B47" s="15">
         <f>IF(A47="","",LEN(A47)-LEN(SUBSTITUTE(A47,".",""))+1)</f>
         <v/>
       </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="14">
+      <c r="D47" s="15">
         <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$7:$A$66,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2046,24 +2095,24 @@
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="15" t="n"/>
+      <c r="I47" s="16" t="n"/>
       <c r="J47" s="7">
         <f>IF(A47="","",IF(COUNTIF($A$7:$A$66,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$7:$A$66,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="17">
         <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="n"/>
-      <c r="B48" s="14">
+      <c r="A48" s="14" t="n"/>
+      <c r="B48" s="15">
         <f>IF(A48="","",LEN(A48)-LEN(SUBSTITUTE(A48,".",""))+1)</f>
         <v/>
       </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$7:$A$66,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2071,24 +2120,24 @@
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="15" t="n"/>
+      <c r="I48" s="16" t="n"/>
       <c r="J48" s="7">
         <f>IF(A48="","",IF(COUNTIF($A$7:$A$66,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$7:$A$66,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="17">
         <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="n"/>
-      <c r="B49" s="14">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="15">
         <f>IF(A49="","",LEN(A49)-LEN(SUBSTITUTE(A49,".",""))+1)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="14">
+      <c r="D49" s="15">
         <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$7:$A$66,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2096,24 +2145,24 @@
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="15" t="n"/>
+      <c r="I49" s="16" t="n"/>
       <c r="J49" s="7">
         <f>IF(A49="","",IF(COUNTIF($A$7:$A$66,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$7:$A$66,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="17">
         <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n"/>
-      <c r="B50" s="14">
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="15">
         <f>IF(A50="","",LEN(A50)-LEN(SUBSTITUTE(A50,".",""))+1)</f>
         <v/>
       </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="14">
+      <c r="D50" s="15">
         <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$7:$A$66,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2121,24 +2170,24 @@
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="15" t="n"/>
+      <c r="I50" s="16" t="n"/>
       <c r="J50" s="7">
         <f>IF(A50="","",IF(COUNTIF($A$7:$A$66,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$7:$A$66,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="17">
         <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="n"/>
-      <c r="B51" s="14">
+      <c r="A51" s="14" t="n"/>
+      <c r="B51" s="15">
         <f>IF(A51="","",LEN(A51)-LEN(SUBSTITUTE(A51,".",""))+1)</f>
         <v/>
       </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="14">
+      <c r="D51" s="15">
         <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$7:$A$66,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2146,24 +2195,24 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="15" t="n"/>
+      <c r="I51" s="16" t="n"/>
       <c r="J51" s="7">
         <f>IF(A51="","",IF(COUNTIF($A$7:$A$66,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$7:$A$66,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="17">
         <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n"/>
-      <c r="B52" s="14">
+      <c r="A52" s="14" t="n"/>
+      <c r="B52" s="15">
         <f>IF(A52="","",LEN(A52)-LEN(SUBSTITUTE(A52,".",""))+1)</f>
         <v/>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="14">
+      <c r="D52" s="15">
         <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$7:$A$66,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2171,24 +2220,24 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="15" t="n"/>
+      <c r="I52" s="16" t="n"/>
       <c r="J52" s="7">
         <f>IF(A52="","",IF(COUNTIF($A$7:$A$66,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$7:$A$66,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="17">
         <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n"/>
-      <c r="B53" s="14">
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="15">
         <f>IF(A53="","",LEN(A53)-LEN(SUBSTITUTE(A53,".",""))+1)</f>
         <v/>
       </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="14">
+      <c r="D53" s="15">
         <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$7:$A$66,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2196,24 +2245,24 @@
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="15" t="n"/>
+      <c r="I53" s="16" t="n"/>
       <c r="J53" s="7">
         <f>IF(A53="","",IF(COUNTIF($A$7:$A$66,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$7:$A$66,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="17">
         <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n"/>
-      <c r="B54" s="14">
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="15">
         <f>IF(A54="","",LEN(A54)-LEN(SUBSTITUTE(A54,".",""))+1)</f>
         <v/>
       </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="14">
+      <c r="D54" s="15">
         <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$7:$A$66,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2221,24 +2270,24 @@
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="15" t="n"/>
+      <c r="I54" s="16" t="n"/>
       <c r="J54" s="7">
         <f>IF(A54="","",IF(COUNTIF($A$7:$A$66,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$7:$A$66,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="17">
         <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n"/>
-      <c r="B55" s="14">
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="15">
         <f>IF(A55="","",LEN(A55)-LEN(SUBSTITUTE(A55,".",""))+1)</f>
         <v/>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="14">
+      <c r="D55" s="15">
         <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$7:$A$66,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2246,24 +2295,24 @@
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="15" t="n"/>
+      <c r="I55" s="16" t="n"/>
       <c r="J55" s="7">
         <f>IF(A55="","",IF(COUNTIF($A$7:$A$66,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$7:$A$66,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="17">
         <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="n"/>
-      <c r="B56" s="14">
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="15">
         <f>IF(A56="","",LEN(A56)-LEN(SUBSTITUTE(A56,".",""))+1)</f>
         <v/>
       </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="14">
+      <c r="D56" s="15">
         <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$7:$A$66,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2271,24 +2320,24 @@
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
-      <c r="I56" s="15" t="n"/>
+      <c r="I56" s="16" t="n"/>
       <c r="J56" s="7">
         <f>IF(A56="","",IF(COUNTIF($A$7:$A$66,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$7:$A$66,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="17">
         <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="n"/>
-      <c r="B57" s="14">
+      <c r="A57" s="14" t="n"/>
+      <c r="B57" s="15">
         <f>IF(A57="","",LEN(A57)-LEN(SUBSTITUTE(A57,".",""))+1)</f>
         <v/>
       </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="14">
+      <c r="D57" s="15">
         <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$7:$A$66,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2296,24 +2345,24 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
-      <c r="I57" s="15" t="n"/>
+      <c r="I57" s="16" t="n"/>
       <c r="J57" s="7">
         <f>IF(A57="","",IF(COUNTIF($A$7:$A$66,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$7:$A$66,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="17">
         <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="n"/>
-      <c r="B58" s="14">
+      <c r="A58" s="14" t="n"/>
+      <c r="B58" s="15">
         <f>IF(A58="","",LEN(A58)-LEN(SUBSTITUTE(A58,".",""))+1)</f>
         <v/>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="14">
+      <c r="D58" s="15">
         <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$7:$A$66,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2321,24 +2370,24 @@
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
-      <c r="I58" s="15" t="n"/>
+      <c r="I58" s="16" t="n"/>
       <c r="J58" s="7">
         <f>IF(A58="","",IF(COUNTIF($A$7:$A$66,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$7:$A$66,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="17">
         <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="n"/>
-      <c r="B59" s="14">
+      <c r="A59" s="14" t="n"/>
+      <c r="B59" s="15">
         <f>IF(A59="","",LEN(A59)-LEN(SUBSTITUTE(A59,".",""))+1)</f>
         <v/>
       </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="14">
+      <c r="D59" s="15">
         <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$7:$A$66,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2346,24 +2395,24 @@
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="15" t="n"/>
+      <c r="I59" s="16" t="n"/>
       <c r="J59" s="7">
         <f>IF(A59="","",IF(COUNTIF($A$7:$A$66,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$7:$A$66,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="17">
         <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="n"/>
-      <c r="B60" s="14">
+      <c r="A60" s="14" t="n"/>
+      <c r="B60" s="15">
         <f>IF(A60="","",LEN(A60)-LEN(SUBSTITUTE(A60,".",""))+1)</f>
         <v/>
       </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="14">
+      <c r="D60" s="15">
         <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$7:$A$66,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2371,24 +2420,24 @@
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
-      <c r="I60" s="15" t="n"/>
+      <c r="I60" s="16" t="n"/>
       <c r="J60" s="7">
         <f>IF(A60="","",IF(COUNTIF($A$7:$A$66,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$7:$A$66,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="17">
         <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="n"/>
-      <c r="B61" s="14">
+      <c r="A61" s="14" t="n"/>
+      <c r="B61" s="15">
         <f>IF(A61="","",LEN(A61)-LEN(SUBSTITUTE(A61,".",""))+1)</f>
         <v/>
       </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="14">
+      <c r="D61" s="15">
         <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$7:$A$66,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2396,24 +2445,24 @@
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
-      <c r="I61" s="15" t="n"/>
+      <c r="I61" s="16" t="n"/>
       <c r="J61" s="7">
         <f>IF(A61="","",IF(COUNTIF($A$7:$A$66,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$7:$A$66,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="17">
         <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n"/>
-      <c r="B62" s="14">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="15">
         <f>IF(A62="","",LEN(A62)-LEN(SUBSTITUTE(A62,".",""))+1)</f>
         <v/>
       </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="14">
+      <c r="D62" s="15">
         <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$7:$A$66,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2421,24 +2470,24 @@
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
-      <c r="I62" s="15" t="n"/>
+      <c r="I62" s="16" t="n"/>
       <c r="J62" s="7">
         <f>IF(A62="","",IF(COUNTIF($A$7:$A$66,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$7:$A$66,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="17">
         <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="n"/>
-      <c r="B63" s="14">
+      <c r="A63" s="14" t="n"/>
+      <c r="B63" s="15">
         <f>IF(A63="","",LEN(A63)-LEN(SUBSTITUTE(A63,".",""))+1)</f>
         <v/>
       </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="14">
+      <c r="D63" s="15">
         <f>IF(A63="","",IF(OR(B63=1,COUNTIF($A$7:$A$66,A63&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2446,24 +2495,24 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
-      <c r="I63" s="15" t="n"/>
+      <c r="I63" s="16" t="n"/>
       <c r="J63" s="7">
         <f>IF(A63="","",IF(COUNTIF($A$7:$A$66,A63)&gt;1,"код повторяется",IF(C63="","нет названия",IF(D63="результат",IF(COUNTIF($A$7:$A$66,A63&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E63="","впишите, что предъявляем",IF(F63="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F63)),ISNUMBER(SEARCH(" и ",F63)),LOWER(F63)="все"),"ответственный — один человек",IF(G63="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="17">
         <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n"/>
-      <c r="B64" s="14">
+      <c r="A64" s="14" t="n"/>
+      <c r="B64" s="15">
         <f>IF(A64="","",LEN(A64)-LEN(SUBSTITUTE(A64,".",""))+1)</f>
         <v/>
       </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="14">
+      <c r="D64" s="15">
         <f>IF(A64="","",IF(OR(B64=1,COUNTIF($A$7:$A$66,A64&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2471,24 +2520,24 @@
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
-      <c r="I64" s="15" t="n"/>
+      <c r="I64" s="16" t="n"/>
       <c r="J64" s="7">
         <f>IF(A64="","",IF(COUNTIF($A$7:$A$66,A64)&gt;1,"код повторяется",IF(C64="","нет названия",IF(D64="результат",IF(COUNTIF($A$7:$A$66,A64&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E64="","впишите, что предъявляем",IF(F64="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F64)),ISNUMBER(SEARCH(" и ",F64)),LOWER(F64)="все"),"ответственный — один человек",IF(G64="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="17">
         <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n"/>
-      <c r="B65" s="14">
+      <c r="A65" s="14" t="n"/>
+      <c r="B65" s="15">
         <f>IF(A65="","",LEN(A65)-LEN(SUBSTITUTE(A65,".",""))+1)</f>
         <v/>
       </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="14">
+      <c r="D65" s="15">
         <f>IF(A65="","",IF(OR(B65=1,COUNTIF($A$7:$A$66,A65&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2496,24 +2545,24 @@
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
-      <c r="I65" s="15" t="n"/>
+      <c r="I65" s="16" t="n"/>
       <c r="J65" s="7">
         <f>IF(A65="","",IF(COUNTIF($A$7:$A$66,A65)&gt;1,"код повторяется",IF(C65="","нет названия",IF(D65="результат",IF(COUNTIF($A$7:$A$66,A65&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E65="","впишите, что предъявляем",IF(F65="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F65)),ISNUMBER(SEARCH(" и ",F65)),LOWER(F65)="все"),"ответственный — один человек",IF(G65="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K65" s="16">
+      <c r="K65" s="17">
         <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="n"/>
-      <c r="B66" s="14">
+      <c r="A66" s="14" t="n"/>
+      <c r="B66" s="15">
         <f>IF(A66="","",LEN(A66)-LEN(SUBSTITUTE(A66,".",""))+1)</f>
         <v/>
       </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="14">
+      <c r="D66" s="15">
         <f>IF(A66="","",IF(OR(B66=1,COUNTIF($A$7:$A$66,A66&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2521,12 +2570,12 @@
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
-      <c r="I66" s="15" t="n"/>
+      <c r="I66" s="16" t="n"/>
       <c r="J66" s="7">
         <f>IF(A66="","",IF(COUNTIF($A$7:$A$66,A66)&gt;1,"код повторяется",IF(C66="","нет названия",IF(D66="результат",IF(COUNTIF($A$7:$A$66,A66&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E66="","впишите, что предъявляем",IF(F66="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F66)),ISNUMBER(SEARCH(" и ",F66)),LOWER(F66)="все"),"ответственный — один человек",IF(G66="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="17">
         <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
         <v/>
       </c>
@@ -2613,44 +2662,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Проект:</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Умный горшок: датчик влажности с индикатором</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Результатов</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Пакетов работ</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Замечаний</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>«Отчёт и защита»</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>«Управление проектом»</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Сумма, недель</t>
         </is>
@@ -2662,27 +2711,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <f>COUNTIFS($B$7:$B$66,1)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="13">
         <f>COUNTIF($D$7:$D$66,"пакет работ")</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <f>COUNTIF($J$7:$J$66,"?*")-COUNTIF($J$7:$J$66,"✓")</f>
         <v/>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*отч*")&gt;0,"✓ есть","добавьте")</f>
         <v/>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*управл*")&gt;0,"✓ есть","добавьте")</f>
         <v/>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <f>ROUND(SUM($K$7:$K$66),1)</f>
         <v/>
       </c>
@@ -2745,12 +2794,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <f>IF(A7="","",LEN(A7)-LEN(SUBSTITUTE(A7,".",""))+1)</f>
         <v/>
       </c>
@@ -2759,7 +2808,7 @@
           <t>Прототип датчика с индикатором</t>
         </is>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$7:$A$66,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2767,23 +2816,23 @@
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="15" t="n"/>
+      <c r="I7" s="16" t="n"/>
       <c r="J7" s="7">
         <f>IF(A7="","",IF(COUNTIF($A$7:$A$66,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$7:$A$66,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="17">
         <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <f>IF(A8="","",LEN(A8)-LEN(SUBSTITUTE(A8,".",""))+1)</f>
         <v/>
       </c>
@@ -2792,7 +2841,7 @@
           <t>Компоненты подобраны и куплены</t>
         </is>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$7:$A$66,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2814,23 +2863,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I8" s="15" t="n"/>
+      <c r="I8" s="16" t="n"/>
       <c r="J8" s="7">
         <f>IF(A8="","",IF(COUNTIF($A$7:$A$66,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$7:$A$66,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="17">
         <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <f>IF(A9="","",LEN(A9)-LEN(SUBSTITUTE(A9,".",""))+1)</f>
         <v/>
       </c>
@@ -2839,7 +2888,7 @@
           <t>Схема собрана и проверена на столе</t>
         </is>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$7:$A$66,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2861,23 +2910,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
+      <c r="I9" s="16" t="n"/>
       <c r="J9" s="7">
         <f>IF(A9="","",IF(COUNTIF($A$7:$A$66,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$7:$A$66,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="17">
         <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <f>IF(A10="","",LEN(A10)-LEN(SUBSTITUTE(A10,".",""))+1)</f>
         <v/>
       </c>
@@ -2886,7 +2935,7 @@
           <t>Программа: порог влажности включает индикатор</t>
         </is>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$7:$A$66,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2908,23 +2957,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I10" s="15" t="n"/>
+      <c r="I10" s="16" t="n"/>
       <c r="J10" s="7">
         <f>IF(A10="","",IF(COUNTIF($A$7:$A$66,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$7:$A$66,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="17">
         <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <f>IF(A11="","",LEN(A11)-LEN(SUBSTITUTE(A11,".",""))+1)</f>
         <v/>
       </c>
@@ -2933,7 +2982,7 @@
           <t>Корпус с индикатором</t>
         </is>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$7:$A$66,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2955,23 +3004,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I11" s="15" t="n"/>
+      <c r="I11" s="16" t="n"/>
       <c r="J11" s="7">
         <f>IF(A11="","",IF(COUNTIF($A$7:$A$66,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$7:$A$66,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="17">
         <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="15">
         <f>IF(A12="","",LEN(A12)-LEN(SUBSTITUTE(A12,".",""))+1)</f>
         <v/>
       </c>
@@ -2980,7 +3029,7 @@
           <t>Испытания</t>
         </is>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$7:$A$66,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -2988,23 +3037,23 @@
       <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="15" t="n"/>
+      <c r="I12" s="16" t="n"/>
       <c r="J12" s="7">
         <f>IF(A12="","",IF(COUNTIF($A$7:$A$66,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$7:$A$66,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="17">
         <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <f>IF(A13="","",LEN(A13)-LEN(SUBSTITUTE(A13,".",""))+1)</f>
         <v/>
       </c>
@@ -3013,7 +3062,7 @@
           <t>Калибровка датчика по контрольному влагомеру</t>
         </is>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$7:$A$66,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3035,23 +3084,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I13" s="15" t="n"/>
+      <c r="I13" s="16" t="n"/>
       <c r="J13" s="7">
         <f>IF(A13="","",IF(COUNTIF($A$7:$A$66,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$7:$A$66,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="17">
         <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="15">
         <f>IF(A14="","",LEN(A14)-LEN(SUBSTITUTE(A14,".",""))+1)</f>
         <v/>
       </c>
@@ -3060,7 +3109,7 @@
           <t>Десять циклов полива на трёх растениях</t>
         </is>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$7:$A$66,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3082,23 +3131,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="16" t="n"/>
       <c r="J14" s="7">
         <f>IF(A14="","",IF(COUNTIF($A$7:$A$66,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$7:$A$66,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="17">
         <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="15">
         <f>IF(A15="","",LEN(A15)-LEN(SUBSTITUTE(A15,".",""))+1)</f>
         <v/>
       </c>
@@ -3107,7 +3156,7 @@
           <t>Проверка с пользователями</t>
         </is>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="15">
         <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$7:$A$66,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3115,23 +3164,23 @@
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="15" t="n"/>
+      <c r="I15" s="16" t="n"/>
       <c r="J15" s="7">
         <f>IF(A15="","",IF(COUNTIF($A$7:$A$66,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$7:$A$66,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="17">
         <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>IF(A16="","",LEN(A16)-LEN(SUBSTITUTE(A16,".",""))+1)</f>
         <v/>
       </c>
@@ -3140,7 +3189,7 @@
           <t>Три владельца растений попробовали прототип</t>
         </is>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$7:$A$66,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3162,23 +3211,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I16" s="15" t="n"/>
+      <c r="I16" s="16" t="n"/>
       <c r="J16" s="7">
         <f>IF(A16="","",IF(COUNTIF($A$7:$A$66,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$7:$A$66,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="17">
         <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>IF(A17="","",LEN(A17)-LEN(SUBSTITUTE(A17,".",""))+1)</f>
         <v/>
       </c>
@@ -3187,7 +3236,7 @@
           <t>Отчёт и защита</t>
         </is>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$7:$A$66,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3195,23 +3244,23 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="15" t="n"/>
+      <c r="I17" s="16" t="n"/>
       <c r="J17" s="7">
         <f>IF(A17="","",IF(COUNTIF($A$7:$A$66,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$7:$A$66,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="17">
         <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="15">
         <f>IF(A18="","",LEN(A18)-LEN(SUBSTITUTE(A18,".",""))+1)</f>
         <v/>
       </c>
@@ -3220,7 +3269,7 @@
           <t>Письменный отчёт</t>
         </is>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$7:$A$66,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3242,23 +3291,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I18" s="15" t="n"/>
+      <c r="I18" s="16" t="n"/>
       <c r="J18" s="7">
         <f>IF(A18="","",IF(COUNTIF($A$7:$A$66,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$7:$A$66,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="17">
         <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <f>IF(A19="","",LEN(A19)-LEN(SUBSTITUTE(A19,".",""))+1)</f>
         <v/>
       </c>
@@ -3267,7 +3316,7 @@
           <t>Презентация и питч</t>
         </is>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$7:$A$66,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3289,23 +3338,23 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I19" s="15" t="n"/>
+      <c r="I19" s="16" t="n"/>
       <c r="J19" s="7">
         <f>IF(A19="","",IF(COUNTIF($A$7:$A$66,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$7:$A$66,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="17">
         <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <f>IF(A20="","",LEN(A20)-LEN(SUBSTITUTE(A20,".",""))+1)</f>
         <v/>
       </c>
@@ -3314,7 +3363,7 @@
           <t>Управление проектом</t>
         </is>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$7:$A$66,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3322,23 +3371,23 @@
       <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="15" t="n"/>
+      <c r="I20" s="16" t="n"/>
       <c r="J20" s="7">
         <f>IF(A20="","",IF(COUNTIF($A$7:$A$66,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$7:$A$66,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="17">
         <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <f>IF(A21="","",LEN(A21)-LEN(SUBSTITUTE(A21,".",""))+1)</f>
         <v/>
       </c>
@@ -3347,7 +3396,7 @@
           <t>Паспорт, план, журнал проекта</t>
         </is>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$7:$A$66,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3367,24 +3416,24 @@
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="15" t="n"/>
+      <c r="I21" s="16" t="n"/>
       <c r="J21" s="7">
         <f>IF(A21="","",IF(COUNTIF($A$7:$A$66,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$7:$A$66,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="17">
         <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="14">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15">
         <f>IF(A22="","",LEN(A22)-LEN(SUBSTITUTE(A22,".",""))+1)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$7:$A$66,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3392,24 +3441,24 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="15" t="n"/>
+      <c r="I22" s="16" t="n"/>
       <c r="J22" s="7">
         <f>IF(A22="","",IF(COUNTIF($A$7:$A$66,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$7:$A$66,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="17">
         <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="14">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15">
         <f>IF(A23="","",LEN(A23)-LEN(SUBSTITUTE(A23,".",""))+1)</f>
         <v/>
       </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$7:$A$66,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3417,24 +3466,24 @@
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
-      <c r="I23" s="15" t="n"/>
+      <c r="I23" s="16" t="n"/>
       <c r="J23" s="7">
         <f>IF(A23="","",IF(COUNTIF($A$7:$A$66,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$7:$A$66,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="17">
         <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="14">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15">
         <f>IF(A24="","",LEN(A24)-LEN(SUBSTITUTE(A24,".",""))+1)</f>
         <v/>
       </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$7:$A$66,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3442,24 +3491,24 @@
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
-      <c r="I24" s="15" t="n"/>
+      <c r="I24" s="16" t="n"/>
       <c r="J24" s="7">
         <f>IF(A24="","",IF(COUNTIF($A$7:$A$66,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$7:$A$66,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="17">
         <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n"/>
-      <c r="B25" s="14">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15">
         <f>IF(A25="","",LEN(A25)-LEN(SUBSTITUTE(A25,".",""))+1)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$7:$A$66,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3467,24 +3516,24 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
-      <c r="I25" s="15" t="n"/>
+      <c r="I25" s="16" t="n"/>
       <c r="J25" s="7">
         <f>IF(A25="","",IF(COUNTIF($A$7:$A$66,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$7:$A$66,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="17">
         <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="n"/>
-      <c r="B26" s="14">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15">
         <f>IF(A26="","",LEN(A26)-LEN(SUBSTITUTE(A26,".",""))+1)</f>
         <v/>
       </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$7:$A$66,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3492,24 +3541,24 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
-      <c r="I26" s="15" t="n"/>
+      <c r="I26" s="16" t="n"/>
       <c r="J26" s="7">
         <f>IF(A26="","",IF(COUNTIF($A$7:$A$66,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$7:$A$66,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="17">
         <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n"/>
-      <c r="B27" s="14">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15">
         <f>IF(A27="","",LEN(A27)-LEN(SUBSTITUTE(A27,".",""))+1)</f>
         <v/>
       </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$7:$A$66,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3517,24 +3566,24 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="15" t="n"/>
+      <c r="I27" s="16" t="n"/>
       <c r="J27" s="7">
         <f>IF(A27="","",IF(COUNTIF($A$7:$A$66,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$7:$A$66,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="17">
         <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n"/>
-      <c r="B28" s="14">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15">
         <f>IF(A28="","",LEN(A28)-LEN(SUBSTITUTE(A28,".",""))+1)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$7:$A$66,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3542,24 +3591,24 @@
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="15" t="n"/>
+      <c r="I28" s="16" t="n"/>
       <c r="J28" s="7">
         <f>IF(A28="","",IF(COUNTIF($A$7:$A$66,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$7:$A$66,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="17">
         <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n"/>
-      <c r="B29" s="14">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15">
         <f>IF(A29="","",LEN(A29)-LEN(SUBSTITUTE(A29,".",""))+1)</f>
         <v/>
       </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$7:$A$66,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3567,24 +3616,24 @@
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="15" t="n"/>
+      <c r="I29" s="16" t="n"/>
       <c r="J29" s="7">
         <f>IF(A29="","",IF(COUNTIF($A$7:$A$66,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$7:$A$66,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="17">
         <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n"/>
-      <c r="B30" s="14">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15">
         <f>IF(A30="","",LEN(A30)-LEN(SUBSTITUTE(A30,".",""))+1)</f>
         <v/>
       </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$7:$A$66,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3592,24 +3641,24 @@
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="15" t="n"/>
+      <c r="I30" s="16" t="n"/>
       <c r="J30" s="7">
         <f>IF(A30="","",IF(COUNTIF($A$7:$A$66,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$7:$A$66,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="17">
         <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="14">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15">
         <f>IF(A31="","",LEN(A31)-LEN(SUBSTITUTE(A31,".",""))+1)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="14">
+      <c r="D31" s="15">
         <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$7:$A$66,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3617,24 +3666,24 @@
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="15" t="n"/>
+      <c r="I31" s="16" t="n"/>
       <c r="J31" s="7">
         <f>IF(A31="","",IF(COUNTIF($A$7:$A$66,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$7:$A$66,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="17">
         <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n"/>
-      <c r="B32" s="14">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15">
         <f>IF(A32="","",LEN(A32)-LEN(SUBSTITUTE(A32,".",""))+1)</f>
         <v/>
       </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$7:$A$66,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3642,24 +3691,24 @@
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="15" t="n"/>
+      <c r="I32" s="16" t="n"/>
       <c r="J32" s="7">
         <f>IF(A32="","",IF(COUNTIF($A$7:$A$66,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$7:$A$66,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="17">
         <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="14">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15">
         <f>IF(A33="","",LEN(A33)-LEN(SUBSTITUTE(A33,".",""))+1)</f>
         <v/>
       </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="14">
+      <c r="D33" s="15">
         <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$7:$A$66,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3667,24 +3716,24 @@
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="15" t="n"/>
+      <c r="I33" s="16" t="n"/>
       <c r="J33" s="7">
         <f>IF(A33="","",IF(COUNTIF($A$7:$A$66,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$7:$A$66,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="17">
         <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n"/>
-      <c r="B34" s="14">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15">
         <f>IF(A34="","",LEN(A34)-LEN(SUBSTITUTE(A34,".",""))+1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$7:$A$66,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3692,24 +3741,24 @@
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="15" t="n"/>
+      <c r="I34" s="16" t="n"/>
       <c r="J34" s="7">
         <f>IF(A34="","",IF(COUNTIF($A$7:$A$66,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$7:$A$66,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="17">
         <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="14">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15">
         <f>IF(A35="","",LEN(A35)-LEN(SUBSTITUTE(A35,".",""))+1)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$7:$A$66,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3717,24 +3766,24 @@
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="15" t="n"/>
+      <c r="I35" s="16" t="n"/>
       <c r="J35" s="7">
         <f>IF(A35="","",IF(COUNTIF($A$7:$A$66,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$7:$A$66,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="17">
         <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n"/>
-      <c r="B36" s="14">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="15">
         <f>IF(A36="","",LEN(A36)-LEN(SUBSTITUTE(A36,".",""))+1)</f>
         <v/>
       </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$7:$A$66,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3742,24 +3791,24 @@
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="15" t="n"/>
+      <c r="I36" s="16" t="n"/>
       <c r="J36" s="7">
         <f>IF(A36="","",IF(COUNTIF($A$7:$A$66,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$7:$A$66,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="17">
         <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
-      <c r="B37" s="14">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="15">
         <f>IF(A37="","",LEN(A37)-LEN(SUBSTITUTE(A37,".",""))+1)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$7:$A$66,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3767,24 +3816,24 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="15" t="n"/>
+      <c r="I37" s="16" t="n"/>
       <c r="J37" s="7">
         <f>IF(A37="","",IF(COUNTIF($A$7:$A$66,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$7:$A$66,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="17">
         <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n"/>
-      <c r="B38" s="14">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15">
         <f>IF(A38="","",LEN(A38)-LEN(SUBSTITUTE(A38,".",""))+1)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$7:$A$66,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3792,24 +3841,24 @@
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
-      <c r="I38" s="15" t="n"/>
+      <c r="I38" s="16" t="n"/>
       <c r="J38" s="7">
         <f>IF(A38="","",IF(COUNTIF($A$7:$A$66,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$7:$A$66,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="17">
         <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="14">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15">
         <f>IF(A39="","",LEN(A39)-LEN(SUBSTITUTE(A39,".",""))+1)</f>
         <v/>
       </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="14">
+      <c r="D39" s="15">
         <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$7:$A$66,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3817,24 +3866,24 @@
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="15" t="n"/>
+      <c r="I39" s="16" t="n"/>
       <c r="J39" s="7">
         <f>IF(A39="","",IF(COUNTIF($A$7:$A$66,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$7:$A$66,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="17">
         <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="14">
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="15">
         <f>IF(A40="","",LEN(A40)-LEN(SUBSTITUTE(A40,".",""))+1)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$7:$A$66,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3842,24 +3891,24 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="15" t="n"/>
+      <c r="I40" s="16" t="n"/>
       <c r="J40" s="7">
         <f>IF(A40="","",IF(COUNTIF($A$7:$A$66,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$7:$A$66,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="17">
         <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n"/>
-      <c r="B41" s="14">
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="15">
         <f>IF(A41="","",LEN(A41)-LEN(SUBSTITUTE(A41,".",""))+1)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="14">
+      <c r="D41" s="15">
         <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$7:$A$66,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3867,24 +3916,24 @@
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="15" t="n"/>
+      <c r="I41" s="16" t="n"/>
       <c r="J41" s="7">
         <f>IF(A41="","",IF(COUNTIF($A$7:$A$66,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$7:$A$66,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="17">
         <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n"/>
-      <c r="B42" s="14">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15">
         <f>IF(A42="","",LEN(A42)-LEN(SUBSTITUTE(A42,".",""))+1)</f>
         <v/>
       </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$7:$A$66,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3892,24 +3941,24 @@
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
-      <c r="I42" s="15" t="n"/>
+      <c r="I42" s="16" t="n"/>
       <c r="J42" s="7">
         <f>IF(A42="","",IF(COUNTIF($A$7:$A$66,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$7:$A$66,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="17">
         <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n"/>
-      <c r="B43" s="14">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15">
         <f>IF(A43="","",LEN(A43)-LEN(SUBSTITUTE(A43,".",""))+1)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="14">
+      <c r="D43" s="15">
         <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$7:$A$66,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3917,24 +3966,24 @@
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
-      <c r="I43" s="15" t="n"/>
+      <c r="I43" s="16" t="n"/>
       <c r="J43" s="7">
         <f>IF(A43="","",IF(COUNTIF($A$7:$A$66,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$7:$A$66,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="17">
         <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="n"/>
-      <c r="B44" s="14">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15">
         <f>IF(A44="","",LEN(A44)-LEN(SUBSTITUTE(A44,".",""))+1)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$7:$A$66,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3942,24 +3991,24 @@
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="15" t="n"/>
+      <c r="I44" s="16" t="n"/>
       <c r="J44" s="7">
         <f>IF(A44="","",IF(COUNTIF($A$7:$A$66,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$7:$A$66,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="17">
         <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="n"/>
-      <c r="B45" s="14">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="15">
         <f>IF(A45="","",LEN(A45)-LEN(SUBSTITUTE(A45,".",""))+1)</f>
         <v/>
       </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="14">
+      <c r="D45" s="15">
         <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$7:$A$66,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3967,24 +4016,24 @@
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="15" t="n"/>
+      <c r="I45" s="16" t="n"/>
       <c r="J45" s="7">
         <f>IF(A45="","",IF(COUNTIF($A$7:$A$66,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$7:$A$66,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="17">
         <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n"/>
-      <c r="B46" s="14">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="15">
         <f>IF(A46="","",LEN(A46)-LEN(SUBSTITUTE(A46,".",""))+1)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$7:$A$66,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -3992,24 +4041,24 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="15" t="n"/>
+      <c r="I46" s="16" t="n"/>
       <c r="J46" s="7">
         <f>IF(A46="","",IF(COUNTIF($A$7:$A$66,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$7:$A$66,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="17">
         <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n"/>
-      <c r="B47" s="14">
+      <c r="A47" s="14" t="n"/>
+      <c r="B47" s="15">
         <f>IF(A47="","",LEN(A47)-LEN(SUBSTITUTE(A47,".",""))+1)</f>
         <v/>
       </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="14">
+      <c r="D47" s="15">
         <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$7:$A$66,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4017,24 +4066,24 @@
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="15" t="n"/>
+      <c r="I47" s="16" t="n"/>
       <c r="J47" s="7">
         <f>IF(A47="","",IF(COUNTIF($A$7:$A$66,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$7:$A$66,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="17">
         <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="n"/>
-      <c r="B48" s="14">
+      <c r="A48" s="14" t="n"/>
+      <c r="B48" s="15">
         <f>IF(A48="","",LEN(A48)-LEN(SUBSTITUTE(A48,".",""))+1)</f>
         <v/>
       </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$7:$A$66,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4042,24 +4091,24 @@
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="15" t="n"/>
+      <c r="I48" s="16" t="n"/>
       <c r="J48" s="7">
         <f>IF(A48="","",IF(COUNTIF($A$7:$A$66,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$7:$A$66,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="17">
         <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="n"/>
-      <c r="B49" s="14">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="15">
         <f>IF(A49="","",LEN(A49)-LEN(SUBSTITUTE(A49,".",""))+1)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="14">
+      <c r="D49" s="15">
         <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$7:$A$66,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4067,24 +4116,24 @@
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="15" t="n"/>
+      <c r="I49" s="16" t="n"/>
       <c r="J49" s="7">
         <f>IF(A49="","",IF(COUNTIF($A$7:$A$66,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$7:$A$66,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="17">
         <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n"/>
-      <c r="B50" s="14">
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="15">
         <f>IF(A50="","",LEN(A50)-LEN(SUBSTITUTE(A50,".",""))+1)</f>
         <v/>
       </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="14">
+      <c r="D50" s="15">
         <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$7:$A$66,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4092,24 +4141,24 @@
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="15" t="n"/>
+      <c r="I50" s="16" t="n"/>
       <c r="J50" s="7">
         <f>IF(A50="","",IF(COUNTIF($A$7:$A$66,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$7:$A$66,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="17">
         <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="n"/>
-      <c r="B51" s="14">
+      <c r="A51" s="14" t="n"/>
+      <c r="B51" s="15">
         <f>IF(A51="","",LEN(A51)-LEN(SUBSTITUTE(A51,".",""))+1)</f>
         <v/>
       </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="14">
+      <c r="D51" s="15">
         <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$7:$A$66,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4117,24 +4166,24 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="15" t="n"/>
+      <c r="I51" s="16" t="n"/>
       <c r="J51" s="7">
         <f>IF(A51="","",IF(COUNTIF($A$7:$A$66,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$7:$A$66,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="17">
         <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n"/>
-      <c r="B52" s="14">
+      <c r="A52" s="14" t="n"/>
+      <c r="B52" s="15">
         <f>IF(A52="","",LEN(A52)-LEN(SUBSTITUTE(A52,".",""))+1)</f>
         <v/>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="14">
+      <c r="D52" s="15">
         <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$7:$A$66,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4142,24 +4191,24 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="15" t="n"/>
+      <c r="I52" s="16" t="n"/>
       <c r="J52" s="7">
         <f>IF(A52="","",IF(COUNTIF($A$7:$A$66,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$7:$A$66,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="17">
         <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n"/>
-      <c r="B53" s="14">
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="15">
         <f>IF(A53="","",LEN(A53)-LEN(SUBSTITUTE(A53,".",""))+1)</f>
         <v/>
       </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="14">
+      <c r="D53" s="15">
         <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$7:$A$66,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4167,24 +4216,24 @@
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="15" t="n"/>
+      <c r="I53" s="16" t="n"/>
       <c r="J53" s="7">
         <f>IF(A53="","",IF(COUNTIF($A$7:$A$66,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$7:$A$66,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="17">
         <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n"/>
-      <c r="B54" s="14">
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="15">
         <f>IF(A54="","",LEN(A54)-LEN(SUBSTITUTE(A54,".",""))+1)</f>
         <v/>
       </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="14">
+      <c r="D54" s="15">
         <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$7:$A$66,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4192,24 +4241,24 @@
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="15" t="n"/>
+      <c r="I54" s="16" t="n"/>
       <c r="J54" s="7">
         <f>IF(A54="","",IF(COUNTIF($A$7:$A$66,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$7:$A$66,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="17">
         <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n"/>
-      <c r="B55" s="14">
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="15">
         <f>IF(A55="","",LEN(A55)-LEN(SUBSTITUTE(A55,".",""))+1)</f>
         <v/>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="14">
+      <c r="D55" s="15">
         <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$7:$A$66,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4217,24 +4266,24 @@
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="15" t="n"/>
+      <c r="I55" s="16" t="n"/>
       <c r="J55" s="7">
         <f>IF(A55="","",IF(COUNTIF($A$7:$A$66,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$7:$A$66,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="17">
         <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="n"/>
-      <c r="B56" s="14">
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="15">
         <f>IF(A56="","",LEN(A56)-LEN(SUBSTITUTE(A56,".",""))+1)</f>
         <v/>
       </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="14">
+      <c r="D56" s="15">
         <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$7:$A$66,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4242,24 +4291,24 @@
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
-      <c r="I56" s="15" t="n"/>
+      <c r="I56" s="16" t="n"/>
       <c r="J56" s="7">
         <f>IF(A56="","",IF(COUNTIF($A$7:$A$66,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$7:$A$66,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="17">
         <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="n"/>
-      <c r="B57" s="14">
+      <c r="A57" s="14" t="n"/>
+      <c r="B57" s="15">
         <f>IF(A57="","",LEN(A57)-LEN(SUBSTITUTE(A57,".",""))+1)</f>
         <v/>
       </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="14">
+      <c r="D57" s="15">
         <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$7:$A$66,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4267,24 +4316,24 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
-      <c r="I57" s="15" t="n"/>
+      <c r="I57" s="16" t="n"/>
       <c r="J57" s="7">
         <f>IF(A57="","",IF(COUNTIF($A$7:$A$66,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$7:$A$66,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="17">
         <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="n"/>
-      <c r="B58" s="14">
+      <c r="A58" s="14" t="n"/>
+      <c r="B58" s="15">
         <f>IF(A58="","",LEN(A58)-LEN(SUBSTITUTE(A58,".",""))+1)</f>
         <v/>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="14">
+      <c r="D58" s="15">
         <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$7:$A$66,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4292,24 +4341,24 @@
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
-      <c r="I58" s="15" t="n"/>
+      <c r="I58" s="16" t="n"/>
       <c r="J58" s="7">
         <f>IF(A58="","",IF(COUNTIF($A$7:$A$66,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$7:$A$66,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="17">
         <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="n"/>
-      <c r="B59" s="14">
+      <c r="A59" s="14" t="n"/>
+      <c r="B59" s="15">
         <f>IF(A59="","",LEN(A59)-LEN(SUBSTITUTE(A59,".",""))+1)</f>
         <v/>
       </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="14">
+      <c r="D59" s="15">
         <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$7:$A$66,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4317,24 +4366,24 @@
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="15" t="n"/>
+      <c r="I59" s="16" t="n"/>
       <c r="J59" s="7">
         <f>IF(A59="","",IF(COUNTIF($A$7:$A$66,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$7:$A$66,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="17">
         <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="n"/>
-      <c r="B60" s="14">
+      <c r="A60" s="14" t="n"/>
+      <c r="B60" s="15">
         <f>IF(A60="","",LEN(A60)-LEN(SUBSTITUTE(A60,".",""))+1)</f>
         <v/>
       </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="14">
+      <c r="D60" s="15">
         <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$7:$A$66,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4342,24 +4391,24 @@
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
-      <c r="I60" s="15" t="n"/>
+      <c r="I60" s="16" t="n"/>
       <c r="J60" s="7">
         <f>IF(A60="","",IF(COUNTIF($A$7:$A$66,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$7:$A$66,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="17">
         <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="n"/>
-      <c r="B61" s="14">
+      <c r="A61" s="14" t="n"/>
+      <c r="B61" s="15">
         <f>IF(A61="","",LEN(A61)-LEN(SUBSTITUTE(A61,".",""))+1)</f>
         <v/>
       </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="14">
+      <c r="D61" s="15">
         <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$7:$A$66,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4367,24 +4416,24 @@
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
-      <c r="I61" s="15" t="n"/>
+      <c r="I61" s="16" t="n"/>
       <c r="J61" s="7">
         <f>IF(A61="","",IF(COUNTIF($A$7:$A$66,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$7:$A$66,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="17">
         <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n"/>
-      <c r="B62" s="14">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="15">
         <f>IF(A62="","",LEN(A62)-LEN(SUBSTITUTE(A62,".",""))+1)</f>
         <v/>
       </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="14">
+      <c r="D62" s="15">
         <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$7:$A$66,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4392,24 +4441,24 @@
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
-      <c r="I62" s="15" t="n"/>
+      <c r="I62" s="16" t="n"/>
       <c r="J62" s="7">
         <f>IF(A62="","",IF(COUNTIF($A$7:$A$66,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$7:$A$66,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="17">
         <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="n"/>
-      <c r="B63" s="14">
+      <c r="A63" s="14" t="n"/>
+      <c r="B63" s="15">
         <f>IF(A63="","",LEN(A63)-LEN(SUBSTITUTE(A63,".",""))+1)</f>
         <v/>
       </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="14">
+      <c r="D63" s="15">
         <f>IF(A63="","",IF(OR(B63=1,COUNTIF($A$7:$A$66,A63&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4417,24 +4466,24 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
-      <c r="I63" s="15" t="n"/>
+      <c r="I63" s="16" t="n"/>
       <c r="J63" s="7">
         <f>IF(A63="","",IF(COUNTIF($A$7:$A$66,A63)&gt;1,"код повторяется",IF(C63="","нет названия",IF(D63="результат",IF(COUNTIF($A$7:$A$66,A63&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E63="","впишите, что предъявляем",IF(F63="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F63)),ISNUMBER(SEARCH(" и ",F63)),LOWER(F63)="все"),"ответственный — один человек",IF(G63="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="17">
         <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n"/>
-      <c r="B64" s="14">
+      <c r="A64" s="14" t="n"/>
+      <c r="B64" s="15">
         <f>IF(A64="","",LEN(A64)-LEN(SUBSTITUTE(A64,".",""))+1)</f>
         <v/>
       </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="14">
+      <c r="D64" s="15">
         <f>IF(A64="","",IF(OR(B64=1,COUNTIF($A$7:$A$66,A64&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4442,24 +4491,24 @@
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
-      <c r="I64" s="15" t="n"/>
+      <c r="I64" s="16" t="n"/>
       <c r="J64" s="7">
         <f>IF(A64="","",IF(COUNTIF($A$7:$A$66,A64)&gt;1,"код повторяется",IF(C64="","нет названия",IF(D64="результат",IF(COUNTIF($A$7:$A$66,A64&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E64="","впишите, что предъявляем",IF(F64="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F64)),ISNUMBER(SEARCH(" и ",F64)),LOWER(F64)="все"),"ответственный — один человек",IF(G64="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="17">
         <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n"/>
-      <c r="B65" s="14">
+      <c r="A65" s="14" t="n"/>
+      <c r="B65" s="15">
         <f>IF(A65="","",LEN(A65)-LEN(SUBSTITUTE(A65,".",""))+1)</f>
         <v/>
       </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="14">
+      <c r="D65" s="15">
         <f>IF(A65="","",IF(OR(B65=1,COUNTIF($A$7:$A$66,A65&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4467,24 +4516,24 @@
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
-      <c r="I65" s="15" t="n"/>
+      <c r="I65" s="16" t="n"/>
       <c r="J65" s="7">
         <f>IF(A65="","",IF(COUNTIF($A$7:$A$66,A65)&gt;1,"код повторяется",IF(C65="","нет названия",IF(D65="результат",IF(COUNTIF($A$7:$A$66,A65&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E65="","впишите, что предъявляем",IF(F65="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F65)),ISNUMBER(SEARCH(" и ",F65)),LOWER(F65)="все"),"ответственный — один человек",IF(G65="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K65" s="16">
+      <c r="K65" s="17">
         <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="n"/>
-      <c r="B66" s="14">
+      <c r="A66" s="14" t="n"/>
+      <c r="B66" s="15">
         <f>IF(A66="","",LEN(A66)-LEN(SUBSTITUTE(A66,".",""))+1)</f>
         <v/>
       </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="14">
+      <c r="D66" s="15">
         <f>IF(A66="","",IF(OR(B66=1,COUNTIF($A$7:$A$66,A66&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
@@ -4492,12 +4541,12 @@
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
-      <c r="I66" s="15" t="n"/>
+      <c r="I66" s="16" t="n"/>
       <c r="J66" s="7">
         <f>IF(A66="","",IF(COUNTIF($A$7:$A$66,A66)&gt;1,"код повторяется",IF(C66="","нет названия",IF(D66="результат",IF(COUNTIF($A$7:$A$66,A66&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E66="","впишите, что предъявляем",IF(F66="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F66)),ISNUMBER(SEARCH(" и ",F66)),LOWER(F66)="все"),"ответственный — один человек",IF(G66="","оцените длительность","✓"))))))))</f>
         <v/>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="17">
         <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
         <v/>
       </c>

--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Пример — умный горшок" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'WBS'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'WBS'!$A$1:$J$66</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Пример — умный горшок'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Пример — умный горшок'!$A$1:$J$66</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'WBS'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'WBS'!$A$1:$J$62</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Пример — умный горшок'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Пример — умный горшок'!$A$1:$J$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,8 +81,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF7F8C9A"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FF005AAA"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -147,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -177,10 +178,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -202,6 +200,12 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FFE70F47"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="FF002C5F"/>
       </font>
       <fill>
@@ -210,12 +214,6 @@
           <bgColor rgb="FFE6EFF8"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFE70F47"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -800,11 +798,11 @@
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="8">
-        <f>IF(A5="","",COUNTIF(WBS!$F$7:$F$66,A5))</f>
+        <f>IF(A5="","",COUNTIF(WBS!$F$3:$F$62,A5))</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IF(A5="","",ROUND(SUMIF(WBS!$F$7:$F$66,A5,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A5="","",ROUND(SUMIF(WBS!$F$3:$F$62,A5,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -817,11 +815,11 @@
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="8">
-        <f>IF(A6="","",COUNTIF(WBS!$F$7:$F$66,A6))</f>
+        <f>IF(A6="","",COUNTIF(WBS!$F$3:$F$62,A6))</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>IF(A6="","",ROUND(SUMIF(WBS!$F$7:$F$66,A6,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A6="","",ROUND(SUMIF(WBS!$F$3:$F$62,A6,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -834,11 +832,11 @@
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="8">
-        <f>IF(A7="","",COUNTIF(WBS!$F$7:$F$66,A7))</f>
+        <f>IF(A7="","",COUNTIF(WBS!$F$3:$F$62,A7))</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>IF(A7="","",ROUND(SUMIF(WBS!$F$7:$F$66,A7,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A7="","",ROUND(SUMIF(WBS!$F$3:$F$62,A7,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -851,11 +849,11 @@
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="8">
-        <f>IF(A8="","",COUNTIF(WBS!$F$7:$F$66,A8))</f>
+        <f>IF(A8="","",COUNTIF(WBS!$F$3:$F$62,A8))</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>IF(A8="","",ROUND(SUMIF(WBS!$F$7:$F$66,A8,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A8="","",ROUND(SUMIF(WBS!$F$3:$F$62,A8,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -868,11 +866,11 @@
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="8">
-        <f>IF(A9="","",COUNTIF(WBS!$F$7:$F$66,A9))</f>
+        <f>IF(A9="","",COUNTIF(WBS!$F$3:$F$62,A9))</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>IF(A9="","",ROUND(SUMIF(WBS!$F$7:$F$66,A9,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A9="","",ROUND(SUMIF(WBS!$F$3:$F$62,A9,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -881,11 +879,11 @@
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="8">
-        <f>IF(A10="","",COUNTIF(WBS!$F$7:$F$66,A10))</f>
+        <f>IF(A10="","",COUNTIF(WBS!$F$3:$F$62,A10))</f>
         <v/>
       </c>
       <c r="D10" s="8">
-        <f>IF(A10="","",ROUND(SUMIF(WBS!$F$7:$F$66,A10,WBS!$K$7:$K$66),1))</f>
+        <f>IF(A10="","",ROUND(SUMIF(WBS!$F$3:$F$62,A10,WBS!$K$3:$K$62),1))</f>
         <v/>
       </c>
       <c r="F10" s="9" t="n"/>
@@ -929,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -945,1683 +943,1603 @@
     <col hidden="1" width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>WBS проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Проект:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="F1" s="12">
+        <f>"Результатов: "&amp;COUNTIFS($B$3:$B$62,1)&amp;"  ·  пакетов: "&amp;COUNTIF($D$3:$D$62,"пакет работ")&amp;"  ·  замечаний: "&amp;(COUNTIF($J$3:$J$62,"?*")-COUNTIF($J$3:$J$62,"✓"))&amp;"  ·  отчёт и защита: "&amp;IF(COUNTIFS($B$3:$B$62,1,$C$3:$C$62,"*отч*")&gt;0,"✓","добавьте")&amp;"  ·  управление проектом: "&amp;IF(COUNTIFS($B$3:$B$62,1,$C$3:$C$62,"*управл*")&gt;0,"✓","добавьте")&amp;"  ·  сумма: "&amp;ROUND(SUM($K$3:$K$62),1)&amp;" нед. по очереди (реальный срок покажет Ганта)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Элемент WBS: результат или пакет работ (существительным)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Что предъявляем: предмет, документ, данные</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Ответственный (один)</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Зависит от (коды) — на следующей паре</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Результатов</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Пакетов работ</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Замечаний</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>«Отчёт и защита»</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>«Управление проектом»</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Сумма, недель</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Сумма — если делать всё по очереди. Реальный срок покажет диаграмма Ганта.</t>
-        </is>
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="14">
+        <f>IF(A3="","",LEN(A3)-LEN(SUBSTITUTE(A3,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="14">
+        <f>IF(A3="","",IF(OR(B3=1,COUNTIF($A$3:$A$62,A3&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="7">
+        <f>IF(A3="","",IF(COUNTIF($A$3:$A$62,A3)&gt;1,"код повторяется",IF(C3="","нет названия",IF(D3="результат",IF(COUNTIF($A$3:$A$62,A3&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E3="","впишите, что предъявляем",IF(F3="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F3)),ISNUMBER(SEARCH(" и ",F3)),LOWER(F3)="все"),"ответственный — один человек",IF(G3="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K3" s="16">
+        <f>IF(AND(D3="пакет работ",ISNUMBER(G3)),G3*IF(LEFT(LOWER(H3),1)="д",1/7,1),0)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
-        <f>COUNTIFS($B$7:$B$66,1)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>COUNTIF($D$7:$D$66,"пакет работ")</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>COUNTIF($J$7:$J$66,"?*")-COUNTIF($J$7:$J$66,"✓")</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*отч*")&gt;0,"✓ есть","добавьте")</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*управл*")&gt;0,"✓ есть","добавьте")</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>ROUND(SUM($K$7:$K$66),1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Уровень</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Элемент WBS: результат или пакет работ (существительным)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Что предъявляем: предмет, документ, данные</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Ответственный (один)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Зависит от (коды) — на следующей паре</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="14">
+        <f>IF(A4="","",LEN(A4)-LEN(SUBSTITUTE(A4,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="14">
+        <f>IF(A4="","",IF(OR(B4=1,COUNTIF($A$3:$A$62,A4&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="7">
+        <f>IF(A4="","",IF(COUNTIF($A$3:$A$62,A4)&gt;1,"код повторяется",IF(C4="","нет названия",IF(D4="результат",IF(COUNTIF($A$3:$A$62,A4&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E4="","впишите, что предъявляем",IF(F4="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F4)),ISNUMBER(SEARCH(" и ",F4)),LOWER(F4)="все"),"ответственный — один человек",IF(G4="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K4" s="16">
+        <f>IF(AND(D4="пакет работ",ISNUMBER(G4)),G4*IF(LEFT(LOWER(H4),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="14">
+        <f>IF(A5="","",LEN(A5)-LEN(SUBSTITUTE(A5,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="14">
+        <f>IF(A5="","",IF(OR(B5=1,COUNTIF($A$3:$A$62,A5&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="7">
+        <f>IF(A5="","",IF(COUNTIF($A$3:$A$62,A5)&gt;1,"код повторяется",IF(C5="","нет названия",IF(D5="результат",IF(COUNTIF($A$3:$A$62,A5&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E5="","впишите, что предъявляем",IF(F5="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F5)),ISNUMBER(SEARCH(" и ",F5)),LOWER(F5)="все"),"ответственный — один человек",IF(G5="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K5" s="16">
+        <f>IF(AND(D5="пакет работ",ISNUMBER(G5)),G5*IF(LEFT(LOWER(H5),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="14">
+        <f>IF(A6="","",LEN(A6)-LEN(SUBSTITUTE(A6,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="14">
+        <f>IF(A6="","",IF(OR(B6=1,COUNTIF($A$3:$A$62,A6&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="7">
+        <f>IF(A6="","",IF(COUNTIF($A$3:$A$62,A6)&gt;1,"код повторяется",IF(C6="","нет названия",IF(D6="результат",IF(COUNTIF($A$3:$A$62,A6&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E6="","впишите, что предъявляем",IF(F6="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F6)),ISNUMBER(SEARCH(" и ",F6)),LOWER(F6)="все"),"ответственный — один человек",IF(G6="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>IF(AND(D6="пакет работ",ISNUMBER(G6)),G6*IF(LEFT(LOWER(H6),1)="д",1/7,1),0)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n"/>
-      <c r="B7" s="15">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="14">
         <f>IF(A7="","",LEN(A7)-LEN(SUBSTITUTE(A7,".",""))+1)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="15">
-        <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$7:$A$66,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D7" s="14">
+        <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$3:$A$62,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="15" t="n"/>
       <c r="J7" s="7">
-        <f>IF(A7="","",IF(COUNTIF($A$7:$A$66,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$7:$A$66,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K7" s="17">
+        <f>IF(A7="","",IF(COUNTIF($A$3:$A$62,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$3:$A$62,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
         <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n"/>
-      <c r="B8" s="15">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="14">
         <f>IF(A8="","",LEN(A8)-LEN(SUBSTITUTE(A8,".",""))+1)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="15">
-        <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$7:$A$66,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D8" s="14">
+        <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$3:$A$62,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="15" t="n"/>
       <c r="J8" s="7">
-        <f>IF(A8="","",IF(COUNTIF($A$7:$A$66,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$7:$A$66,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="17">
+        <f>IF(A8="","",IF(COUNTIF($A$3:$A$62,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$3:$A$62,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
         <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="15">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="14">
         <f>IF(A9="","",LEN(A9)-LEN(SUBSTITUTE(A9,".",""))+1)</f>
         <v/>
       </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="15">
-        <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$7:$A$66,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D9" s="14">
+        <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$3:$A$62,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="15" t="n"/>
       <c r="J9" s="7">
-        <f>IF(A9="","",IF(COUNTIF($A$7:$A$66,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$7:$A$66,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="17">
+        <f>IF(A9="","",IF(COUNTIF($A$3:$A$62,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$3:$A$62,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="16">
         <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n"/>
-      <c r="B10" s="15">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="14">
         <f>IF(A10="","",LEN(A10)-LEN(SUBSTITUTE(A10,".",""))+1)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="15">
-        <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$7:$A$66,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D10" s="14">
+        <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$3:$A$62,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="15" t="n"/>
       <c r="J10" s="7">
-        <f>IF(A10="","",IF(COUNTIF($A$7:$A$66,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$7:$A$66,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="17">
+        <f>IF(A10="","",IF(COUNTIF($A$3:$A$62,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$3:$A$62,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
         <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n"/>
-      <c r="B11" s="15">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="14">
         <f>IF(A11="","",LEN(A11)-LEN(SUBSTITUTE(A11,".",""))+1)</f>
         <v/>
       </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="15">
-        <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$7:$A$66,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D11" s="14">
+        <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$3:$A$62,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="15" t="n"/>
       <c r="J11" s="7">
-        <f>IF(A11="","",IF(COUNTIF($A$7:$A$66,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$7:$A$66,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="17">
+        <f>IF(A11="","",IF(COUNTIF($A$3:$A$62,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$3:$A$62,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="16">
         <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n"/>
-      <c r="B12" s="15">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="14">
         <f>IF(A12="","",LEN(A12)-LEN(SUBSTITUTE(A12,".",""))+1)</f>
         <v/>
       </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="15">
-        <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$7:$A$66,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D12" s="14">
+        <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$3:$A$62,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="15" t="n"/>
       <c r="J12" s="7">
-        <f>IF(A12="","",IF(COUNTIF($A$7:$A$66,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$7:$A$66,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="17">
+        <f>IF(A12="","",IF(COUNTIF($A$3:$A$62,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$3:$A$62,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
         <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n"/>
-      <c r="B13" s="15">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="14">
         <f>IF(A13="","",LEN(A13)-LEN(SUBSTITUTE(A13,".",""))+1)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="15">
-        <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$7:$A$66,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D13" s="14">
+        <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$3:$A$62,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="15" t="n"/>
       <c r="J13" s="7">
-        <f>IF(A13="","",IF(COUNTIF($A$7:$A$66,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$7:$A$66,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="17">
+        <f>IF(A13="","",IF(COUNTIF($A$3:$A$62,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$3:$A$62,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="16">
         <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="15">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="14">
         <f>IF(A14="","",LEN(A14)-LEN(SUBSTITUTE(A14,".",""))+1)</f>
         <v/>
       </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="15">
-        <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$7:$A$66,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D14" s="14">
+        <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$3:$A$62,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="15" t="n"/>
       <c r="J14" s="7">
-        <f>IF(A14="","",IF(COUNTIF($A$7:$A$66,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$7:$A$66,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="17">
+        <f>IF(A14="","",IF(COUNTIF($A$3:$A$62,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$3:$A$62,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="16">
         <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n"/>
-      <c r="B15" s="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="14">
         <f>IF(A15="","",LEN(A15)-LEN(SUBSTITUTE(A15,".",""))+1)</f>
         <v/>
       </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="15">
-        <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$7:$A$66,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D15" s="14">
+        <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$3:$A$62,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="15" t="n"/>
       <c r="J15" s="7">
-        <f>IF(A15="","",IF(COUNTIF($A$7:$A$66,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$7:$A$66,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K15" s="17">
+        <f>IF(A15="","",IF(COUNTIF($A$3:$A$62,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$3:$A$62,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K15" s="16">
         <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="15">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="14">
         <f>IF(A16="","",LEN(A16)-LEN(SUBSTITUTE(A16,".",""))+1)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="15">
-        <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$7:$A$66,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D16" s="14">
+        <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$3:$A$62,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="15" t="n"/>
       <c r="J16" s="7">
-        <f>IF(A16="","",IF(COUNTIF($A$7:$A$66,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$7:$A$66,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K16" s="17">
+        <f>IF(A16="","",IF(COUNTIF($A$3:$A$62,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$3:$A$62,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K16" s="16">
         <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="15">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="14">
         <f>IF(A17="","",LEN(A17)-LEN(SUBSTITUTE(A17,".",""))+1)</f>
         <v/>
       </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="15">
-        <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$7:$A$66,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D17" s="14">
+        <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$3:$A$62,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="15" t="n"/>
       <c r="J17" s="7">
-        <f>IF(A17="","",IF(COUNTIF($A$7:$A$66,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$7:$A$66,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
+        <f>IF(A17="","",IF(COUNTIF($A$3:$A$62,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$3:$A$62,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
         <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="15">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14">
         <f>IF(A18="","",LEN(A18)-LEN(SUBSTITUTE(A18,".",""))+1)</f>
         <v/>
       </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="15">
-        <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$7:$A$66,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D18" s="14">
+        <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$3:$A$62,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="15" t="n"/>
       <c r="J18" s="7">
-        <f>IF(A18="","",IF(COUNTIF($A$7:$A$66,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$7:$A$66,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K18" s="17">
+        <f>IF(A18="","",IF(COUNTIF($A$3:$A$62,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$3:$A$62,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K18" s="16">
         <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n"/>
-      <c r="B19" s="15">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="14">
         <f>IF(A19="","",LEN(A19)-LEN(SUBSTITUTE(A19,".",""))+1)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="15">
-        <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$7:$A$66,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D19" s="14">
+        <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$3:$A$62,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="15" t="n"/>
       <c r="J19" s="7">
-        <f>IF(A19="","",IF(COUNTIF($A$7:$A$66,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$7:$A$66,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K19" s="17">
+        <f>IF(A19="","",IF(COUNTIF($A$3:$A$62,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$3:$A$62,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K19" s="16">
         <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n"/>
-      <c r="B20" s="15">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="14">
         <f>IF(A20="","",LEN(A20)-LEN(SUBSTITUTE(A20,".",""))+1)</f>
         <v/>
       </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="15">
-        <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$7:$A$66,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D20" s="14">
+        <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$3:$A$62,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="15" t="n"/>
       <c r="J20" s="7">
-        <f>IF(A20="","",IF(COUNTIF($A$7:$A$66,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$7:$A$66,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K20" s="17">
+        <f>IF(A20="","",IF(COUNTIF($A$3:$A$62,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$3:$A$62,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K20" s="16">
         <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n"/>
-      <c r="B21" s="15">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="14">
         <f>IF(A21="","",LEN(A21)-LEN(SUBSTITUTE(A21,".",""))+1)</f>
         <v/>
       </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="15">
-        <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$7:$A$66,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D21" s="14">
+        <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$3:$A$62,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="15" t="n"/>
       <c r="J21" s="7">
-        <f>IF(A21="","",IF(COUNTIF($A$7:$A$66,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$7:$A$66,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K21" s="17">
+        <f>IF(A21="","",IF(COUNTIF($A$3:$A$62,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$3:$A$62,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K21" s="16">
         <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="14">
         <f>IF(A22="","",LEN(A22)-LEN(SUBSTITUTE(A22,".",""))+1)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="15">
-        <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$7:$A$66,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D22" s="14">
+        <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$3:$A$62,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="7">
-        <f>IF(A22="","",IF(COUNTIF($A$7:$A$66,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$7:$A$66,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K22" s="17">
+        <f>IF(A22="","",IF(COUNTIF($A$3:$A$62,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$3:$A$62,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K22" s="16">
         <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="14">
         <f>IF(A23="","",LEN(A23)-LEN(SUBSTITUTE(A23,".",""))+1)</f>
         <v/>
       </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="15">
-        <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$7:$A$66,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D23" s="14">
+        <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$3:$A$62,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="7">
-        <f>IF(A23="","",IF(COUNTIF($A$7:$A$66,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$7:$A$66,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K23" s="17">
+        <f>IF(A23="","",IF(COUNTIF($A$3:$A$62,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$3:$A$62,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K23" s="16">
         <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="14">
         <f>IF(A24="","",LEN(A24)-LEN(SUBSTITUTE(A24,".",""))+1)</f>
         <v/>
       </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="15">
-        <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$7:$A$66,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D24" s="14">
+        <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$3:$A$62,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="7">
-        <f>IF(A24="","",IF(COUNTIF($A$7:$A$66,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$7:$A$66,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
+        <f>IF(A24="","",IF(COUNTIF($A$3:$A$62,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$3:$A$62,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
         <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="14">
         <f>IF(A25="","",LEN(A25)-LEN(SUBSTITUTE(A25,".",""))+1)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="15">
-        <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$7:$A$66,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D25" s="14">
+        <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$3:$A$62,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="15" t="n"/>
       <c r="J25" s="7">
-        <f>IF(A25="","",IF(COUNTIF($A$7:$A$66,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$7:$A$66,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
+        <f>IF(A25="","",IF(COUNTIF($A$3:$A$62,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$3:$A$62,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
         <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="14">
         <f>IF(A26="","",LEN(A26)-LEN(SUBSTITUTE(A26,".",""))+1)</f>
         <v/>
       </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="15">
-        <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$7:$A$66,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D26" s="14">
+        <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$3:$A$62,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="15" t="n"/>
       <c r="J26" s="7">
-        <f>IF(A26="","",IF(COUNTIF($A$7:$A$66,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$7:$A$66,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
+        <f>IF(A26="","",IF(COUNTIF($A$3:$A$62,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$3:$A$62,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
         <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n"/>
-      <c r="B27" s="15">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="14">
         <f>IF(A27="","",LEN(A27)-LEN(SUBSTITUTE(A27,".",""))+1)</f>
         <v/>
       </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="15">
-        <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$7:$A$66,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D27" s="14">
+        <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$3:$A$62,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="15" t="n"/>
       <c r="J27" s="7">
-        <f>IF(A27="","",IF(COUNTIF($A$7:$A$66,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$7:$A$66,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
+        <f>IF(A27="","",IF(COUNTIF($A$3:$A$62,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$3:$A$62,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
         <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="15">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="14">
         <f>IF(A28="","",LEN(A28)-LEN(SUBSTITUTE(A28,".",""))+1)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="15">
-        <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$7:$A$66,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D28" s="14">
+        <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$3:$A$62,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="15" t="n"/>
       <c r="J28" s="7">
-        <f>IF(A28="","",IF(COUNTIF($A$7:$A$66,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$7:$A$66,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
+        <f>IF(A28="","",IF(COUNTIF($A$3:$A$62,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$3:$A$62,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
         <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="15">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="14">
         <f>IF(A29="","",LEN(A29)-LEN(SUBSTITUTE(A29,".",""))+1)</f>
         <v/>
       </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="15">
-        <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$7:$A$66,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D29" s="14">
+        <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$3:$A$62,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="15" t="n"/>
       <c r="J29" s="7">
-        <f>IF(A29="","",IF(COUNTIF($A$7:$A$66,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$7:$A$66,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
+        <f>IF(A29="","",IF(COUNTIF($A$3:$A$62,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$3:$A$62,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
         <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="n"/>
-      <c r="B30" s="15">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="14">
         <f>IF(A30="","",LEN(A30)-LEN(SUBSTITUTE(A30,".",""))+1)</f>
         <v/>
       </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="15">
-        <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$7:$A$66,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D30" s="14">
+        <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$3:$A$62,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="15" t="n"/>
       <c r="J30" s="7">
-        <f>IF(A30="","",IF(COUNTIF($A$7:$A$66,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$7:$A$66,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
+        <f>IF(A30="","",IF(COUNTIF($A$3:$A$62,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$3:$A$62,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
         <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="n"/>
-      <c r="B31" s="15">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="14">
         <f>IF(A31="","",LEN(A31)-LEN(SUBSTITUTE(A31,".",""))+1)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="15">
-        <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$7:$A$66,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D31" s="14">
+        <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$3:$A$62,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="15" t="n"/>
       <c r="J31" s="7">
-        <f>IF(A31="","",IF(COUNTIF($A$7:$A$66,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$7:$A$66,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
+        <f>IF(A31="","",IF(COUNTIF($A$3:$A$62,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$3:$A$62,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
         <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="15">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="14">
         <f>IF(A32="","",LEN(A32)-LEN(SUBSTITUTE(A32,".",""))+1)</f>
         <v/>
       </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="15">
-        <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$7:$A$66,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D32" s="14">
+        <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$3:$A$62,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="15" t="n"/>
       <c r="J32" s="7">
-        <f>IF(A32="","",IF(COUNTIF($A$7:$A$66,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$7:$A$66,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
+        <f>IF(A32="","",IF(COUNTIF($A$3:$A$62,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$3:$A$62,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
         <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="n"/>
-      <c r="B33" s="15">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="14">
         <f>IF(A33="","",LEN(A33)-LEN(SUBSTITUTE(A33,".",""))+1)</f>
         <v/>
       </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="15">
-        <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$7:$A$66,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D33" s="14">
+        <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$3:$A$62,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="15" t="n"/>
       <c r="J33" s="7">
-        <f>IF(A33="","",IF(COUNTIF($A$7:$A$66,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$7:$A$66,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
+        <f>IF(A33="","",IF(COUNTIF($A$3:$A$62,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$3:$A$62,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K33" s="16">
         <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="15">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="14">
         <f>IF(A34="","",LEN(A34)-LEN(SUBSTITUTE(A34,".",""))+1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="15">
-        <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$7:$A$66,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D34" s="14">
+        <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$3:$A$62,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="15" t="n"/>
       <c r="J34" s="7">
-        <f>IF(A34="","",IF(COUNTIF($A$7:$A$66,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$7:$A$66,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K34" s="17">
+        <f>IF(A34="","",IF(COUNTIF($A$3:$A$62,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$3:$A$62,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
         <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n"/>
-      <c r="B35" s="15">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="14">
         <f>IF(A35="","",LEN(A35)-LEN(SUBSTITUTE(A35,".",""))+1)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="15">
-        <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$7:$A$66,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D35" s="14">
+        <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$3:$A$62,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="15" t="n"/>
       <c r="J35" s="7">
-        <f>IF(A35="","",IF(COUNTIF($A$7:$A$66,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$7:$A$66,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
+        <f>IF(A35="","",IF(COUNTIF($A$3:$A$62,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$3:$A$62,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
         <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="15">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="14">
         <f>IF(A36="","",LEN(A36)-LEN(SUBSTITUTE(A36,".",""))+1)</f>
         <v/>
       </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="15">
-        <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$7:$A$66,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D36" s="14">
+        <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$3:$A$62,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="15" t="n"/>
       <c r="J36" s="7">
-        <f>IF(A36="","",IF(COUNTIF($A$7:$A$66,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$7:$A$66,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
+        <f>IF(A36="","",IF(COUNTIF($A$3:$A$62,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$3:$A$62,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
         <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="15">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="14">
         <f>IF(A37="","",LEN(A37)-LEN(SUBSTITUTE(A37,".",""))+1)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="15">
-        <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$7:$A$66,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D37" s="14">
+        <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$3:$A$62,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="15" t="n"/>
       <c r="J37" s="7">
-        <f>IF(A37="","",IF(COUNTIF($A$7:$A$66,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$7:$A$66,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
+        <f>IF(A37="","",IF(COUNTIF($A$3:$A$62,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$3:$A$62,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
         <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="15">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="14">
         <f>IF(A38="","",LEN(A38)-LEN(SUBSTITUTE(A38,".",""))+1)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="15">
-        <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$7:$A$66,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D38" s="14">
+        <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$3:$A$62,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="15" t="n"/>
       <c r="J38" s="7">
-        <f>IF(A38="","",IF(COUNTIF($A$7:$A$66,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$7:$A$66,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K38" s="17">
+        <f>IF(A38="","",IF(COUNTIF($A$3:$A$62,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$3:$A$62,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K38" s="16">
         <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="15">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="14">
         <f>IF(A39="","",LEN(A39)-LEN(SUBSTITUTE(A39,".",""))+1)</f>
         <v/>
       </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="15">
-        <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$7:$A$66,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D39" s="14">
+        <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$3:$A$62,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="15" t="n"/>
       <c r="J39" s="7">
-        <f>IF(A39="","",IF(COUNTIF($A$7:$A$66,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$7:$A$66,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K39" s="17">
+        <f>IF(A39="","",IF(COUNTIF($A$3:$A$62,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$3:$A$62,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K39" s="16">
         <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="15">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="14">
         <f>IF(A40="","",LEN(A40)-LEN(SUBSTITUTE(A40,".",""))+1)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="15">
-        <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$7:$A$66,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D40" s="14">
+        <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$3:$A$62,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="15" t="n"/>
       <c r="J40" s="7">
-        <f>IF(A40="","",IF(COUNTIF($A$7:$A$66,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$7:$A$66,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K40" s="17">
+        <f>IF(A40="","",IF(COUNTIF($A$3:$A$62,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$3:$A$62,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
         <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="15">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="14">
         <f>IF(A41="","",LEN(A41)-LEN(SUBSTITUTE(A41,".",""))+1)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="15">
-        <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$7:$A$66,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D41" s="14">
+        <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$3:$A$62,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="15" t="n"/>
       <c r="J41" s="7">
-        <f>IF(A41="","",IF(COUNTIF($A$7:$A$66,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$7:$A$66,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K41" s="17">
+        <f>IF(A41="","",IF(COUNTIF($A$3:$A$62,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$3:$A$62,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K41" s="16">
         <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="15">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="14">
         <f>IF(A42="","",LEN(A42)-LEN(SUBSTITUTE(A42,".",""))+1)</f>
         <v/>
       </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="15">
-        <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$7:$A$66,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D42" s="14">
+        <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$3:$A$62,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="15" t="n"/>
       <c r="J42" s="7">
-        <f>IF(A42="","",IF(COUNTIF($A$7:$A$66,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$7:$A$66,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K42" s="17">
+        <f>IF(A42="","",IF(COUNTIF($A$3:$A$62,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$3:$A$62,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K42" s="16">
         <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="15">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="14">
         <f>IF(A43="","",LEN(A43)-LEN(SUBSTITUTE(A43,".",""))+1)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="15">
-        <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$7:$A$66,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D43" s="14">
+        <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$3:$A$62,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="15" t="n"/>
       <c r="J43" s="7">
-        <f>IF(A43="","",IF(COUNTIF($A$7:$A$66,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$7:$A$66,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K43" s="17">
+        <f>IF(A43="","",IF(COUNTIF($A$3:$A$62,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$3:$A$62,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K43" s="16">
         <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="n"/>
-      <c r="B44" s="15">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="14">
         <f>IF(A44="","",LEN(A44)-LEN(SUBSTITUTE(A44,".",""))+1)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="15">
-        <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$7:$A$66,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D44" s="14">
+        <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$3:$A$62,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="7">
-        <f>IF(A44="","",IF(COUNTIF($A$7:$A$66,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$7:$A$66,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K44" s="17">
+        <f>IF(A44="","",IF(COUNTIF($A$3:$A$62,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$3:$A$62,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K44" s="16">
         <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="15">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="14">
         <f>IF(A45="","",LEN(A45)-LEN(SUBSTITUTE(A45,".",""))+1)</f>
         <v/>
       </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="15">
-        <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$7:$A$66,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D45" s="14">
+        <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$3:$A$62,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="15" t="n"/>
       <c r="J45" s="7">
-        <f>IF(A45="","",IF(COUNTIF($A$7:$A$66,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$7:$A$66,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K45" s="17">
+        <f>IF(A45="","",IF(COUNTIF($A$3:$A$62,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$3:$A$62,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K45" s="16">
         <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="n"/>
-      <c r="B46" s="15">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="14">
         <f>IF(A46="","",LEN(A46)-LEN(SUBSTITUTE(A46,".",""))+1)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="15">
-        <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$7:$A$66,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D46" s="14">
+        <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$3:$A$62,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="7">
-        <f>IF(A46="","",IF(COUNTIF($A$7:$A$66,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$7:$A$66,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K46" s="17">
+        <f>IF(A46="","",IF(COUNTIF($A$3:$A$62,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$3:$A$62,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K46" s="16">
         <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="14">
         <f>IF(A47="","",LEN(A47)-LEN(SUBSTITUTE(A47,".",""))+1)</f>
         <v/>
       </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="15">
-        <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$7:$A$66,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D47" s="14">
+        <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$3:$A$62,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="15" t="n"/>
       <c r="J47" s="7">
-        <f>IF(A47="","",IF(COUNTIF($A$7:$A$66,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$7:$A$66,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K47" s="17">
+        <f>IF(A47="","",IF(COUNTIF($A$3:$A$62,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$3:$A$62,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K47" s="16">
         <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="n"/>
-      <c r="B48" s="15">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="14">
         <f>IF(A48="","",LEN(A48)-LEN(SUBSTITUTE(A48,".",""))+1)</f>
         <v/>
       </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="15">
-        <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$7:$A$66,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D48" s="14">
+        <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$3:$A$62,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="15" t="n"/>
       <c r="J48" s="7">
-        <f>IF(A48="","",IF(COUNTIF($A$7:$A$66,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$7:$A$66,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K48" s="17">
+        <f>IF(A48="","",IF(COUNTIF($A$3:$A$62,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$3:$A$62,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K48" s="16">
         <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="n"/>
-      <c r="B49" s="15">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="14">
         <f>IF(A49="","",LEN(A49)-LEN(SUBSTITUTE(A49,".",""))+1)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="15">
-        <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$7:$A$66,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D49" s="14">
+        <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$3:$A$62,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="15" t="n"/>
       <c r="J49" s="7">
-        <f>IF(A49="","",IF(COUNTIF($A$7:$A$66,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$7:$A$66,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K49" s="17">
+        <f>IF(A49="","",IF(COUNTIF($A$3:$A$62,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$3:$A$62,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K49" s="16">
         <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n"/>
-      <c r="B50" s="15">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="14">
         <f>IF(A50="","",LEN(A50)-LEN(SUBSTITUTE(A50,".",""))+1)</f>
         <v/>
       </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="15">
-        <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$7:$A$66,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D50" s="14">
+        <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$3:$A$62,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="15" t="n"/>
       <c r="J50" s="7">
-        <f>IF(A50="","",IF(COUNTIF($A$7:$A$66,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$7:$A$66,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K50" s="17">
+        <f>IF(A50="","",IF(COUNTIF($A$3:$A$62,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$3:$A$62,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K50" s="16">
         <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="15">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="14">
         <f>IF(A51="","",LEN(A51)-LEN(SUBSTITUTE(A51,".",""))+1)</f>
         <v/>
       </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="15">
-        <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$7:$A$66,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D51" s="14">
+        <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$3:$A$62,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="15" t="n"/>
       <c r="J51" s="7">
-        <f>IF(A51="","",IF(COUNTIF($A$7:$A$66,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$7:$A$66,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K51" s="17">
+        <f>IF(A51="","",IF(COUNTIF($A$3:$A$62,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$3:$A$62,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K51" s="16">
         <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="n"/>
-      <c r="B52" s="15">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="14">
         <f>IF(A52="","",LEN(A52)-LEN(SUBSTITUTE(A52,".",""))+1)</f>
         <v/>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="15">
-        <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$7:$A$66,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D52" s="14">
+        <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$3:$A$62,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="15" t="n"/>
       <c r="J52" s="7">
-        <f>IF(A52="","",IF(COUNTIF($A$7:$A$66,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$7:$A$66,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K52" s="17">
+        <f>IF(A52="","",IF(COUNTIF($A$3:$A$62,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$3:$A$62,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K52" s="16">
         <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="15">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="14">
         <f>IF(A53="","",LEN(A53)-LEN(SUBSTITUTE(A53,".",""))+1)</f>
         <v/>
       </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="15">
-        <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$7:$A$66,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D53" s="14">
+        <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$3:$A$62,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="15" t="n"/>
       <c r="J53" s="7">
-        <f>IF(A53="","",IF(COUNTIF($A$7:$A$66,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$7:$A$66,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K53" s="17">
+        <f>IF(A53="","",IF(COUNTIF($A$3:$A$62,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$3:$A$62,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K53" s="16">
         <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="15">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="14">
         <f>IF(A54="","",LEN(A54)-LEN(SUBSTITUTE(A54,".",""))+1)</f>
         <v/>
       </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="15">
-        <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$7:$A$66,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D54" s="14">
+        <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$3:$A$62,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="15" t="n"/>
       <c r="J54" s="7">
-        <f>IF(A54="","",IF(COUNTIF($A$7:$A$66,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$7:$A$66,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K54" s="17">
+        <f>IF(A54="","",IF(COUNTIF($A$3:$A$62,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$3:$A$62,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K54" s="16">
         <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="15">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="14">
         <f>IF(A55="","",LEN(A55)-LEN(SUBSTITUTE(A55,".",""))+1)</f>
         <v/>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="15">
-        <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$7:$A$66,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D55" s="14">
+        <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$3:$A$62,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="15" t="n"/>
       <c r="J55" s="7">
-        <f>IF(A55="","",IF(COUNTIF($A$7:$A$66,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$7:$A$66,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K55" s="17">
+        <f>IF(A55="","",IF(COUNTIF($A$3:$A$62,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$3:$A$62,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K55" s="16">
         <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="15">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="14">
         <f>IF(A56="","",LEN(A56)-LEN(SUBSTITUTE(A56,".",""))+1)</f>
         <v/>
       </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="15">
-        <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$7:$A$66,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D56" s="14">
+        <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$3:$A$62,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="15" t="n"/>
       <c r="J56" s="7">
-        <f>IF(A56="","",IF(COUNTIF($A$7:$A$66,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$7:$A$66,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K56" s="17">
+        <f>IF(A56="","",IF(COUNTIF($A$3:$A$62,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$3:$A$62,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K56" s="16">
         <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="n"/>
-      <c r="B57" s="15">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="14">
         <f>IF(A57="","",LEN(A57)-LEN(SUBSTITUTE(A57,".",""))+1)</f>
         <v/>
       </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="15">
-        <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$7:$A$66,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D57" s="14">
+        <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$3:$A$62,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="15" t="n"/>
       <c r="J57" s="7">
-        <f>IF(A57="","",IF(COUNTIF($A$7:$A$66,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$7:$A$66,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K57" s="17">
+        <f>IF(A57="","",IF(COUNTIF($A$3:$A$62,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$3:$A$62,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K57" s="16">
         <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="n"/>
-      <c r="B58" s="15">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="14">
         <f>IF(A58="","",LEN(A58)-LEN(SUBSTITUTE(A58,".",""))+1)</f>
         <v/>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="15">
-        <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$7:$A$66,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D58" s="14">
+        <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$3:$A$62,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="15" t="n"/>
       <c r="J58" s="7">
-        <f>IF(A58="","",IF(COUNTIF($A$7:$A$66,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$7:$A$66,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K58" s="17">
+        <f>IF(A58="","",IF(COUNTIF($A$3:$A$62,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$3:$A$62,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K58" s="16">
         <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="15">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="14">
         <f>IF(A59="","",LEN(A59)-LEN(SUBSTITUTE(A59,".",""))+1)</f>
         <v/>
       </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="15">
-        <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$7:$A$66,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D59" s="14">
+        <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$3:$A$62,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="15" t="n"/>
       <c r="J59" s="7">
-        <f>IF(A59="","",IF(COUNTIF($A$7:$A$66,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$7:$A$66,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K59" s="17">
+        <f>IF(A59="","",IF(COUNTIF($A$3:$A$62,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$3:$A$62,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K59" s="16">
         <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="n"/>
-      <c r="B60" s="15">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="14">
         <f>IF(A60="","",LEN(A60)-LEN(SUBSTITUTE(A60,".",""))+1)</f>
         <v/>
       </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="15">
-        <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$7:$A$66,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D60" s="14">
+        <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$3:$A$62,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="15" t="n"/>
       <c r="J60" s="7">
-        <f>IF(A60="","",IF(COUNTIF($A$7:$A$66,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$7:$A$66,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K60" s="17">
+        <f>IF(A60="","",IF(COUNTIF($A$3:$A$62,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$3:$A$62,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K60" s="16">
         <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="n"/>
-      <c r="B61" s="15">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="14">
         <f>IF(A61="","",LEN(A61)-LEN(SUBSTITUTE(A61,".",""))+1)</f>
         <v/>
       </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="15">
-        <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$7:$A$66,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D61" s="14">
+        <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$3:$A$62,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="15" t="n"/>
       <c r="J61" s="7">
-        <f>IF(A61="","",IF(COUNTIF($A$7:$A$66,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$7:$A$66,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K61" s="17">
+        <f>IF(A61="","",IF(COUNTIF($A$3:$A$62,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$3:$A$62,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K61" s="16">
         <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="n"/>
-      <c r="B62" s="15">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="14">
         <f>IF(A62="","",LEN(A62)-LEN(SUBSTITUTE(A62,".",""))+1)</f>
         <v/>
       </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="15">
-        <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$7:$A$66,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D62" s="14">
+        <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$3:$A$62,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="15" t="n"/>
       <c r="J62" s="7">
-        <f>IF(A62="","",IF(COUNTIF($A$7:$A$66,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$7:$A$66,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K62" s="17">
+        <f>IF(A62="","",IF(COUNTIF($A$3:$A$62,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$3:$A$62,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K62" s="16">
         <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="n"/>
-      <c r="B63" s="15">
-        <f>IF(A63="","",LEN(A63)-LEN(SUBSTITUTE(A63,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="15">
-        <f>IF(A63="","",IF(OR(B63=1,COUNTIF($A$7:$A$66,A63&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="16" t="n"/>
-      <c r="J63" s="7">
-        <f>IF(A63="","",IF(COUNTIF($A$7:$A$66,A63)&gt;1,"код повторяется",IF(C63="","нет названия",IF(D63="результат",IF(COUNTIF($A$7:$A$66,A63&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E63="","впишите, что предъявляем",IF(F63="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F63)),ISNUMBER(SEARCH(" и ",F63)),LOWER(F63)="все"),"ответственный — один человек",IF(G63="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K63" s="17">
-        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="n"/>
-      <c r="B64" s="15">
-        <f>IF(A64="","",LEN(A64)-LEN(SUBSTITUTE(A64,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="15">
-        <f>IF(A64="","",IF(OR(B64=1,COUNTIF($A$7:$A$66,A64&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="7">
-        <f>IF(A64="","",IF(COUNTIF($A$7:$A$66,A64)&gt;1,"код повторяется",IF(C64="","нет названия",IF(D64="результат",IF(COUNTIF($A$7:$A$66,A64&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E64="","впишите, что предъявляем",IF(F64="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F64)),ISNUMBER(SEARCH(" и ",F64)),LOWER(F64)="все"),"ответственный — один человек",IF(G64="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K64" s="17">
-        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="n"/>
-      <c r="B65" s="15">
-        <f>IF(A65="","",LEN(A65)-LEN(SUBSTITUTE(A65,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="15">
-        <f>IF(A65="","",IF(OR(B65=1,COUNTIF($A$7:$A$66,A65&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="16" t="n"/>
-      <c r="J65" s="7">
-        <f>IF(A65="","",IF(COUNTIF($A$7:$A$66,A65)&gt;1,"код повторяется",IF(C65="","нет названия",IF(D65="результат",IF(COUNTIF($A$7:$A$66,A65&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E65="","впишите, что предъявляем",IF(F65="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F65)),ISNUMBER(SEARCH(" и ",F65)),LOWER(F65)="все"),"ответственный — один человек",IF(G65="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K65" s="17">
-        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="n"/>
-      <c r="B66" s="15">
-        <f>IF(A66="","",LEN(A66)-LEN(SUBSTITUTE(A66,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="15">
-        <f>IF(A66="","",IF(OR(B66=1,COUNTIF($A$7:$A$66,A66&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="7">
-        <f>IF(A66="","",IF(COUNTIF($A$7:$A$66,A66)&gt;1,"код повторяется",IF(C66="","нет названия",IF(D66="результат",IF(COUNTIF($A$7:$A$66,A66&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E66="","впишите, что предъявляем",IF(F66="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F66)),ISNUMBER(SEARCH(" и ",F66)),LOWER(F66)="все"),"ответственный — один человек",IF(G66="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K66" s="17">
-        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+  <mergeCells count="2">
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:J66">
+  <conditionalFormatting sqref="F1">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$D7="результат"</formula>
+      <formula>OR(ISNUMBER(SEARCH("добавьте",$F$1)),COUNTIF($J$3:$J$62,"?*")-COUNTIF($J$3:$J$62,"✓")&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J66">
+  <conditionalFormatting sqref="A3:J62">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(J7&lt;&gt;"",J7&lt;&gt;"✓")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>J7="✓"</formula>
+      <formula>$D3="результат"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E4="добавьте"</formula>
+  <conditionalFormatting sqref="J3:J62">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(J3&lt;&gt;"",J3&lt;&gt;"✓")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>F4="добавьте"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>D4&gt;0</formula>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>J3="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
+    <dataValidation sqref="H3:H62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
       <formula1>"недель,дней"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ответственный" error="Этого человека нет на листе «Команда». Ответственный — один человек." type="list" errorStyle="warning">
+    <dataValidation sqref="F3:F62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ответственный" error="Этого человека нет на листе «Команда». Ответственный — один человек." type="list" errorStyle="warning">
       <formula1>Команда!$A$5:$A$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -2638,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2654,247 +2572,355 @@
     <col hidden="1" width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Пример: WBS умного горшка</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Проект:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Умный горшок: датчик влажности с индикатором</t>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Умный горшок: датчик влажности с индикатором (пример)</t>
+        </is>
+      </c>
+      <c r="F1" s="12">
+        <f>"Результатов: "&amp;COUNTIFS($B$3:$B$62,1)&amp;"  ·  пакетов: "&amp;COUNTIF($D$3:$D$62,"пакет работ")&amp;"  ·  замечаний: "&amp;(COUNTIF($J$3:$J$62,"?*")-COUNTIF($J$3:$J$62,"✓"))&amp;"  ·  отчёт и защита: "&amp;IF(COUNTIFS($B$3:$B$62,1,$C$3:$C$62,"*отч*")&gt;0,"✓","добавьте")&amp;"  ·  управление проектом: "&amp;IF(COUNTIFS($B$3:$B$62,1,$C$3:$C$62,"*управл*")&gt;0,"✓","добавьте")&amp;"  ·  сумма: "&amp;ROUND(SUM($K$3:$K$62),1)&amp;" нед. по очереди (реальный срок покажет Ганта)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Элемент WBS: результат или пакет работ (существительным)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Что предъявляем: предмет, документ, данные</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Ответственный (один)</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Зависит от (коды) — на следующей паре</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>недель</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Результатов</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Пакетов работ</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Замечаний</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>«Отчёт и защита»</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>«Управление проектом»</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Сумма, недель</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Сумма — если делать всё по очереди. Реальный срок покажет диаграмма Ганта.</t>
-        </is>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="14">
+        <f>IF(A3="","",LEN(A3)-LEN(SUBSTITUTE(A3,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Прототип датчика с индикатором</t>
+        </is>
+      </c>
+      <c r="D3" s="14">
+        <f>IF(A3="","",IF(OR(B3=1,COUNTIF($A$3:$A$62,A3&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="7">
+        <f>IF(A3="","",IF(COUNTIF($A$3:$A$62,A3)&gt;1,"код повторяется",IF(C3="","нет названия",IF(D3="результат",IF(COUNTIF($A$3:$A$62,A3&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E3="","впишите, что предъявляем",IF(F3="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F3)),ISNUMBER(SEARCH(" и ",F3)),LOWER(F3)="все"),"ответственный — один человек",IF(G3="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K3" s="16">
+        <f>IF(AND(D3="пакет работ",ISNUMBER(G3)),G3*IF(LEFT(LOWER(H3),1)="д",1/7,1),0)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
-        <f>COUNTIFS($B$7:$B$66,1)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>COUNTIF($D$7:$D$66,"пакет работ")</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>COUNTIF($J$7:$J$66,"?*")-COUNTIF($J$7:$J$66,"✓")</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*отч*")&gt;0,"✓ есть","добавьте")</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>IF(COUNTIFS($B$7:$B$66,1,$C$7:$C$66,"*управл*")&gt;0,"✓ есть","добавьте")</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>ROUND(SUM($K$7:$K$66),1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Уровень</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Элемент WBS: результат или пакет работ (существительным)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Что предъявляем: предмет, документ, данные</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Ответственный (один)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Зависит от (коды) — на следующей паре</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="14">
+        <f>IF(A4="","",LEN(A4)-LEN(SUBSTITUTE(A4,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Компоненты подобраны и куплены</t>
+        </is>
+      </c>
+      <c r="D4" s="14">
+        <f>IF(A4="","",IF(OR(B4=1,COUNTIF($A$3:$A$62,A4&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>список компонентов с ценами, не дороже 1500 ₽</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>аналитик</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>недель</t>
         </is>
       </c>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="7">
+        <f>IF(A4="","",IF(COUNTIF($A$3:$A$62,A4)&gt;1,"код повторяется",IF(C4="","нет названия",IF(D4="результат",IF(COUNTIF($A$3:$A$62,A4&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E4="","впишите, что предъявляем",IF(F4="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F4)),ISNUMBER(SEARCH(" и ",F4)),LOWER(F4)="все"),"ответственный — один человек",IF(G4="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K4" s="16">
+        <f>IF(AND(D4="пакет работ",ISNUMBER(G4)),G4*IF(LEFT(LOWER(H4),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B5" s="14">
+        <f>IF(A5="","",LEN(A5)-LEN(SUBSTITUTE(A5,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Схема собрана и проверена на столе</t>
+        </is>
+      </c>
+      <c r="D5" s="14">
+        <f>IF(A5="","",IF(OR(B5=1,COUNTIF($A$3:$A$62,A5&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>фото схемы, показания на трёх образцах почвы</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>технический эксперт</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="7">
+        <f>IF(A5="","",IF(COUNTIF($A$3:$A$62,A5)&gt;1,"код повторяется",IF(C5="","нет названия",IF(D5="результат",IF(COUNTIF($A$3:$A$62,A5&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E5="","впишите, что предъявляем",IF(F5="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F5)),ISNUMBER(SEARCH(" и ",F5)),LOWER(F5)="все"),"ответственный — один человек",IF(G5="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K5" s="16">
+        <f>IF(AND(D5="пакет работ",ISNUMBER(G5)),G5*IF(LEFT(LOWER(H5),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B6" s="14">
+        <f>IF(A6="","",LEN(A6)-LEN(SUBSTITUTE(A6,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Программа: порог влажности включает индикатор</t>
+        </is>
+      </c>
+      <c r="D6" s="14">
+        <f>IF(A6="","",IF(OR(B6=1,COUNTIF($A$3:$A$62,A6&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>код программы</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>технический эксперт</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="7">
+        <f>IF(A6="","",IF(COUNTIF($A$3:$A$62,A6)&gt;1,"код повторяется",IF(C6="","нет названия",IF(D6="результат",IF(COUNTIF($A$3:$A$62,A6&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E6="","впишите, что предъявляем",IF(F6="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F6)),ISNUMBER(SEARCH(" и ",F6)),LOWER(F6)="все"),"ответственный — один человек",IF(G6="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>IF(AND(D6="пакет работ",ISNUMBER(G6)),G6*IF(LEFT(LOWER(H6),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B7" s="14">
         <f>IF(A7="","",LEN(A7)-LEN(SUBSTITUTE(A7,".",""))+1)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Прототип датчика с индикатором</t>
-        </is>
-      </c>
-      <c r="D7" s="15">
-        <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$7:$A$66,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="16" t="n"/>
+          <t>Корпус с индикатором</t>
+        </is>
+      </c>
+      <c r="D7" s="14">
+        <f>IF(A7="","",IF(OR(B7=1,COUNTIF($A$3:$A$62,A7&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>корпус, установленный в горшок</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>лидер</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="n"/>
       <c r="J7" s="7">
-        <f>IF(A7="","",IF(COUNTIF($A$7:$A$66,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$7:$A$66,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K7" s="17">
+        <f>IF(A7="","",IF(COUNTIF($A$3:$A$62,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$3:$A$62,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
         <f>IF(AND(D7="пакет работ",ISNUMBER(G7)),G7*IF(LEFT(LOWER(H7),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="14">
         <f>IF(A8="","",LEN(A8)-LEN(SUBSTITUTE(A8,".",""))+1)</f>
         <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Компоненты подобраны и куплены</t>
-        </is>
-      </c>
-      <c r="D8" s="15">
-        <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$7:$A$66,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>список компонентов с ценами, не дороже 1500 ₽</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>аналитик</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="n"/>
+          <t>Испытания</t>
+        </is>
+      </c>
+      <c r="D8" s="14">
+        <f>IF(A8="","",IF(OR(B8=1,COUNTIF($A$3:$A$62,A8&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="15" t="n"/>
       <c r="J8" s="7">
-        <f>IF(A8="","",IF(COUNTIF($A$7:$A$66,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$7:$A$66,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="17">
+        <f>IF(A8="","",IF(COUNTIF($A$3:$A$62,A8)&gt;1,"код повторяется",IF(C8="","нет названия",IF(D8="результат",IF(COUNTIF($A$3:$A$62,A8&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E8="","впишите, что предъявляем",IF(F8="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F8)),ISNUMBER(SEARCH(" и ",F8)),LOWER(F8)="все"),"ответственный — один человек",IF(G8="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
         <f>IF(AND(D8="пакет работ",ISNUMBER(G8)),G8*IF(LEFT(LOWER(H8),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
         <f>IF(A9="","",LEN(A9)-LEN(SUBSTITUTE(A9,".",""))+1)</f>
         <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Схема собрана и проверена на столе</t>
-        </is>
-      </c>
-      <c r="D9" s="15">
-        <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$7:$A$66,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
+          <t>Калибровка датчика по контрольному влагомеру</t>
+        </is>
+      </c>
+      <c r="D9" s="14">
+        <f>IF(A9="","",IF(OR(B9=1,COUNTIF($A$3:$A$62,A9&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>фото схемы, показания на трёх образцах почвы</t>
+          <t>таблица соответствия показаний</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2910,1686 +2936,1498 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="15" t="n"/>
       <c r="J9" s="7">
-        <f>IF(A9="","",IF(COUNTIF($A$7:$A$66,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$7:$A$66,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="17">
+        <f>IF(A9="","",IF(COUNTIF($A$3:$A$62,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$3:$A$62,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="16">
         <f>IF(AND(D9="пакет работ",ISNUMBER(G9)),G9*IF(LEFT(LOWER(H9),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
         <f>IF(A10="","",LEN(A10)-LEN(SUBSTITUTE(A10,".",""))+1)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Программа: порог влажности включает индикатор</t>
-        </is>
-      </c>
-      <c r="D10" s="15">
-        <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$7:$A$66,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
+          <t>Десять циклов полива на трёх растениях</t>
+        </is>
+      </c>
+      <c r="D10" s="14">
+        <f>IF(A10="","",IF(OR(B10=1,COUNTIF($A$3:$A$62,A10&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>код программы</t>
+          <t>протокол испытаний</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>технический эксперт</t>
+          <t>аналитик</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="7">
+        <f>IF(A10="","",IF(COUNTIF($A$3:$A$62,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$3:$A$62,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>IF(A11="","",LEN(A11)-LEN(SUBSTITUTE(A11,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Проверка с пользователями</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
+        <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$3:$A$62,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="7">
+        <f>IF(A11="","",IF(COUNTIF($A$3:$A$62,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$3:$A$62,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="16">
+        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <f>IF(A12="","",LEN(A12)-LEN(SUBSTITUTE(A12,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Три владельца растений попробовали прототип</t>
+        </is>
+      </c>
+      <c r="D12" s="14">
+        <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$3:$A$62,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>записи разговоров, цитаты</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>коммуникатор</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>недель</t>
         </is>
       </c>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="7">
-        <f>IF(A10="","",IF(COUNTIF($A$7:$A$66,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$7:$A$66,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="17">
-        <f>IF(AND(D10="пакет работ",ISNUMBER(G10)),G10*IF(LEFT(LOWER(H10),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="B11" s="15">
-        <f>IF(A11="","",LEN(A11)-LEN(SUBSTITUTE(A11,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Корпус с индикатором</t>
-        </is>
-      </c>
-      <c r="D11" s="15">
-        <f>IF(A11="","",IF(OR(B11=1,COUNTIF($A$7:$A$66,A11&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>корпус, установленный в горшок</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="7">
+        <f>IF(A12="","",IF(COUNTIF($A$3:$A$62,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$3:$A$62,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
+        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>IF(A13="","",LEN(A13)-LEN(SUBSTITUTE(A13,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт и защита</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$3:$A$62,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="7">
+        <f>IF(A13="","",IF(COUNTIF($A$3:$A$62,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$3:$A$62,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="16">
+        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>IF(A14="","",LEN(A14)-LEN(SUBSTITUTE(A14,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Письменный отчёт</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
+        <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$3:$A$62,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>отчёт</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>аналитик</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="7">
+        <f>IF(A14="","",IF(COUNTIF($A$3:$A$62,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$3:$A$62,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="16">
+        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IF(A15="","",LEN(A15)-LEN(SUBSTITUTE(A15,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Презентация и питч</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$3:$A$62,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>презентация, отрепетированный питч</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>коммуникатор</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>недель</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="7">
+        <f>IF(A15="","",IF(COUNTIF($A$3:$A$62,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$3:$A$62,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K15" s="16">
+        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <f>IF(A16="","",LEN(A16)-LEN(SUBSTITUTE(A16,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Управление проектом</t>
+        </is>
+      </c>
+      <c r="D16" s="14">
+        <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$3:$A$62,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="7">
+        <f>IF(A16="","",IF(COUNTIF($A$3:$A$62,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$3:$A$62,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <f>IF(A17="","",LEN(A17)-LEN(SUBSTITUTE(A17,".",""))+1)</f>
+        <v/>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Паспорт, план, журнал проекта</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$3:$A$62,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>документы; журнал — запись каждую неделю</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>лидер</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="7">
-        <f>IF(A11="","",IF(COUNTIF($A$7:$A$66,A11)&gt;1,"код повторяется",IF(C11="","нет названия",IF(D11="результат",IF(COUNTIF($A$7:$A$66,A11&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E11="","впишите, что предъявляем",IF(F11="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F11)),ISNUMBER(SEARCH(" и ",F11)),LOWER(F11)="все"),"ответственный — один человек",IF(G11="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="17">
-        <f>IF(AND(D11="пакет работ",ISNUMBER(G11)),G11*IF(LEFT(LOWER(H11),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" s="15">
-        <f>IF(A12="","",LEN(A12)-LEN(SUBSTITUTE(A12,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Испытания</t>
-        </is>
-      </c>
-      <c r="D12" s="15">
-        <f>IF(A12="","",IF(OR(B12=1,COUNTIF($A$7:$A$66,A12&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="7">
-        <f>IF(A12="","",IF(COUNTIF($A$7:$A$66,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$7:$A$66,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="17">
-        <f>IF(AND(D12="пакет работ",ISNUMBER(G12)),G12*IF(LEFT(LOWER(H12),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B13" s="15">
-        <f>IF(A13="","",LEN(A13)-LEN(SUBSTITUTE(A13,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Калибровка датчика по контрольному влагомеру</t>
-        </is>
-      </c>
-      <c r="D13" s="15">
-        <f>IF(A13="","",IF(OR(B13=1,COUNTIF($A$7:$A$66,A13&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>таблица соответствия показаний</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>технический эксперт</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="7">
-        <f>IF(A13="","",IF(COUNTIF($A$7:$A$66,A13)&gt;1,"код повторяется",IF(C13="","нет названия",IF(D13="результат",IF(COUNTIF($A$7:$A$66,A13&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E13="","впишите, что предъявляем",IF(F13="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F13)),ISNUMBER(SEARCH(" и ",F13)),LOWER(F13)="все"),"ответственный — один человек",IF(G13="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="17">
-        <f>IF(AND(D13="пакет работ",ISNUMBER(G13)),G13*IF(LEFT(LOWER(H13),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <f>IF(A14="","",LEN(A14)-LEN(SUBSTITUTE(A14,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Десять циклов полива на трёх растениях</t>
-        </is>
-      </c>
-      <c r="D14" s="15">
-        <f>IF(A14="","",IF(OR(B14=1,COUNTIF($A$7:$A$66,A14&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>протокол испытаний</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>аналитик</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="7">
-        <f>IF(A14="","",IF(COUNTIF($A$7:$A$66,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$7:$A$66,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="17">
-        <f>IF(AND(D14="пакет работ",ISNUMBER(G14)),G14*IF(LEFT(LOWER(H14),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <f>IF(A15="","",LEN(A15)-LEN(SUBSTITUTE(A15,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Проверка с пользователями</t>
-        </is>
-      </c>
-      <c r="D15" s="15">
-        <f>IF(A15="","",IF(OR(B15=1,COUNTIF($A$7:$A$66,A15&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="7">
-        <f>IF(A15="","",IF(COUNTIF($A$7:$A$66,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$7:$A$66,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K15" s="17">
-        <f>IF(AND(D15="пакет работ",ISNUMBER(G15)),G15*IF(LEFT(LOWER(H15),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B16" s="15">
-        <f>IF(A16="","",LEN(A16)-LEN(SUBSTITUTE(A16,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Три владельца растений попробовали прототип</t>
-        </is>
-      </c>
-      <c r="D16" s="15">
-        <f>IF(A16="","",IF(OR(B16=1,COUNTIF($A$7:$A$66,A16&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>записи разговоров, цитаты</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>коммуникатор</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="7">
-        <f>IF(A16="","",IF(COUNTIF($A$7:$A$66,A16)&gt;1,"код повторяется",IF(C16="","нет названия",IF(D16="результат",IF(COUNTIF($A$7:$A$66,A16&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E16="","впишите, что предъявляем",IF(F16="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F16)),ISNUMBER(SEARCH(" и ",F16)),LOWER(F16)="все"),"ответственный — один человек",IF(G16="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K16" s="17">
-        <f>IF(AND(D16="пакет работ",ISNUMBER(G16)),G16*IF(LEFT(LOWER(H16),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B17" s="15">
-        <f>IF(A17="","",LEN(A17)-LEN(SUBSTITUTE(A17,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт и защита</t>
-        </is>
-      </c>
-      <c r="D17" s="15">
-        <f>IF(A17="","",IF(OR(B17=1,COUNTIF($A$7:$A$66,A17&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>весь проект</t>
+        </is>
+      </c>
       <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="15" t="n"/>
       <c r="J17" s="7">
-        <f>IF(A17="","",IF(COUNTIF($A$7:$A$66,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$7:$A$66,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
+        <f>IF(A17="","",IF(COUNTIF($A$3:$A$62,A17)&gt;1,"код повторяется",IF(C17="","нет названия",IF(D17="результат",IF(COUNTIF($A$3:$A$62,A17&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E17="","впишите, что предъявляем",IF(F17="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F17)),ISNUMBER(SEARCH(" и ",F17)),LOWER(F17)="все"),"ответственный — один человек",IF(G17="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
         <f>IF(AND(D17="пакет работ",ISNUMBER(G17)),G17*IF(LEFT(LOWER(H17),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14">
         <f>IF(A18="","",LEN(A18)-LEN(SUBSTITUTE(A18,".",""))+1)</f>
         <v/>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Письменный отчёт</t>
-        </is>
-      </c>
-      <c r="D18" s="15">
-        <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$7:$A$66,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>отчёт</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>аналитик</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="14">
+        <f>IF(A18="","",IF(OR(B18=1,COUNTIF($A$3:$A$62,A18&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="15" t="n"/>
       <c r="J18" s="7">
-        <f>IF(A18="","",IF(COUNTIF($A$7:$A$66,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$7:$A$66,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K18" s="17">
+        <f>IF(A18="","",IF(COUNTIF($A$3:$A$62,A18)&gt;1,"код повторяется",IF(C18="","нет названия",IF(D18="результат",IF(COUNTIF($A$3:$A$62,A18&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E18="","впишите, что предъявляем",IF(F18="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F18)),ISNUMBER(SEARCH(" и ",F18)),LOWER(F18)="все"),"ответственный — один человек",IF(G18="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K18" s="16">
         <f>IF(AND(D18="пакет работ",ISNUMBER(G18)),G18*IF(LEFT(LOWER(H18),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="14">
         <f>IF(A19="","",LEN(A19)-LEN(SUBSTITUTE(A19,".",""))+1)</f>
         <v/>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Презентация и питч</t>
-        </is>
-      </c>
-      <c r="D19" s="15">
-        <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$7:$A$66,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>презентация, отрепетированный питч</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>коммуникатор</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>недель</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="14">
+        <f>IF(A19="","",IF(OR(B19=1,COUNTIF($A$3:$A$62,A19&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="15" t="n"/>
       <c r="J19" s="7">
-        <f>IF(A19="","",IF(COUNTIF($A$7:$A$66,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$7:$A$66,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K19" s="17">
+        <f>IF(A19="","",IF(COUNTIF($A$3:$A$62,A19)&gt;1,"код повторяется",IF(C19="","нет названия",IF(D19="результат",IF(COUNTIF($A$3:$A$62,A19&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E19="","впишите, что предъявляем",IF(F19="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F19)),ISNUMBER(SEARCH(" и ",F19)),LOWER(F19)="все"),"ответственный — один человек",IF(G19="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K19" s="16">
         <f>IF(AND(D19="пакет работ",ISNUMBER(G19)),G19*IF(LEFT(LOWER(H19),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="14">
         <f>IF(A20="","",LEN(A20)-LEN(SUBSTITUTE(A20,".",""))+1)</f>
         <v/>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Управление проектом</t>
-        </is>
-      </c>
-      <c r="D20" s="15">
-        <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$7:$A$66,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="14">
+        <f>IF(A20="","",IF(OR(B20=1,COUNTIF($A$3:$A$62,A20&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="16" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="15" t="n"/>
       <c r="J20" s="7">
-        <f>IF(A20="","",IF(COUNTIF($A$7:$A$66,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$7:$A$66,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K20" s="17">
+        <f>IF(A20="","",IF(COUNTIF($A$3:$A$62,A20)&gt;1,"код повторяется",IF(C20="","нет названия",IF(D20="результат",IF(COUNTIF($A$3:$A$62,A20&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E20="","впишите, что предъявляем",IF(F20="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F20)),ISNUMBER(SEARCH(" и ",F20)),LOWER(F20)="все"),"ответственный — один человек",IF(G20="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K20" s="16">
         <f>IF(AND(D20="пакет работ",ISNUMBER(G20)),G20*IF(LEFT(LOWER(H20),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="14">
         <f>IF(A21="","",LEN(A21)-LEN(SUBSTITUTE(A21,".",""))+1)</f>
         <v/>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Паспорт, план, журнал проекта</t>
-        </is>
-      </c>
-      <c r="D21" s="15">
-        <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$7:$A$66,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>документы; журнал — запись каждую неделю</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>лидер</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>весь проект</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="16" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="14">
+        <f>IF(A21="","",IF(OR(B21=1,COUNTIF($A$3:$A$62,A21&amp;".*")&gt;0),"результат","пакет работ"))</f>
+        <v/>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="15" t="n"/>
       <c r="J21" s="7">
-        <f>IF(A21="","",IF(COUNTIF($A$7:$A$66,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$7:$A$66,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K21" s="17">
+        <f>IF(A21="","",IF(COUNTIF($A$3:$A$62,A21)&gt;1,"код повторяется",IF(C21="","нет названия",IF(D21="результат",IF(COUNTIF($A$3:$A$62,A21&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E21="","впишите, что предъявляем",IF(F21="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F21)),ISNUMBER(SEARCH(" и ",F21)),LOWER(F21)="все"),"ответственный — один человек",IF(G21="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K21" s="16">
         <f>IF(AND(D21="пакет работ",ISNUMBER(G21)),G21*IF(LEFT(LOWER(H21),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="14">
         <f>IF(A22="","",LEN(A22)-LEN(SUBSTITUTE(A22,".",""))+1)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="15">
-        <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$7:$A$66,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D22" s="14">
+        <f>IF(A22="","",IF(OR(B22=1,COUNTIF($A$3:$A$62,A22&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="7">
-        <f>IF(A22="","",IF(COUNTIF($A$7:$A$66,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$7:$A$66,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K22" s="17">
+        <f>IF(A22="","",IF(COUNTIF($A$3:$A$62,A22)&gt;1,"код повторяется",IF(C22="","нет названия",IF(D22="результат",IF(COUNTIF($A$3:$A$62,A22&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E22="","впишите, что предъявляем",IF(F22="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F22)),ISNUMBER(SEARCH(" и ",F22)),LOWER(F22)="все"),"ответственный — один человек",IF(G22="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K22" s="16">
         <f>IF(AND(D22="пакет работ",ISNUMBER(G22)),G22*IF(LEFT(LOWER(H22),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="14">
         <f>IF(A23="","",LEN(A23)-LEN(SUBSTITUTE(A23,".",""))+1)</f>
         <v/>
       </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="15">
-        <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$7:$A$66,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D23" s="14">
+        <f>IF(A23="","",IF(OR(B23=1,COUNTIF($A$3:$A$62,A23&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="7">
-        <f>IF(A23="","",IF(COUNTIF($A$7:$A$66,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$7:$A$66,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K23" s="17">
+        <f>IF(A23="","",IF(COUNTIF($A$3:$A$62,A23)&gt;1,"код повторяется",IF(C23="","нет названия",IF(D23="результат",IF(COUNTIF($A$3:$A$62,A23&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E23="","впишите, что предъявляем",IF(F23="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F23)),ISNUMBER(SEARCH(" и ",F23)),LOWER(F23)="все"),"ответственный — один человек",IF(G23="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K23" s="16">
         <f>IF(AND(D23="пакет работ",ISNUMBER(G23)),G23*IF(LEFT(LOWER(H23),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="14">
         <f>IF(A24="","",LEN(A24)-LEN(SUBSTITUTE(A24,".",""))+1)</f>
         <v/>
       </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="15">
-        <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$7:$A$66,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D24" s="14">
+        <f>IF(A24="","",IF(OR(B24=1,COUNTIF($A$3:$A$62,A24&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="7">
-        <f>IF(A24="","",IF(COUNTIF($A$7:$A$66,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$7:$A$66,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
+        <f>IF(A24="","",IF(COUNTIF($A$3:$A$62,A24)&gt;1,"код повторяется",IF(C24="","нет названия",IF(D24="результат",IF(COUNTIF($A$3:$A$62,A24&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E24="","впишите, что предъявляем",IF(F24="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F24)),ISNUMBER(SEARCH(" и ",F24)),LOWER(F24)="все"),"ответственный — один человек",IF(G24="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
         <f>IF(AND(D24="пакет работ",ISNUMBER(G24)),G24*IF(LEFT(LOWER(H24),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="14">
         <f>IF(A25="","",LEN(A25)-LEN(SUBSTITUTE(A25,".",""))+1)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="15">
-        <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$7:$A$66,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D25" s="14">
+        <f>IF(A25="","",IF(OR(B25=1,COUNTIF($A$3:$A$62,A25&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="15" t="n"/>
       <c r="J25" s="7">
-        <f>IF(A25="","",IF(COUNTIF($A$7:$A$66,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$7:$A$66,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
+        <f>IF(A25="","",IF(COUNTIF($A$3:$A$62,A25)&gt;1,"код повторяется",IF(C25="","нет названия",IF(D25="результат",IF(COUNTIF($A$3:$A$62,A25&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E25="","впишите, что предъявляем",IF(F25="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F25)),ISNUMBER(SEARCH(" и ",F25)),LOWER(F25)="все"),"ответственный — один человек",IF(G25="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
         <f>IF(AND(D25="пакет работ",ISNUMBER(G25)),G25*IF(LEFT(LOWER(H25),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="14">
         <f>IF(A26="","",LEN(A26)-LEN(SUBSTITUTE(A26,".",""))+1)</f>
         <v/>
       </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="15">
-        <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$7:$A$66,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D26" s="14">
+        <f>IF(A26="","",IF(OR(B26=1,COUNTIF($A$3:$A$62,A26&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="15" t="n"/>
       <c r="J26" s="7">
-        <f>IF(A26="","",IF(COUNTIF($A$7:$A$66,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$7:$A$66,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
+        <f>IF(A26="","",IF(COUNTIF($A$3:$A$62,A26)&gt;1,"код повторяется",IF(C26="","нет названия",IF(D26="результат",IF(COUNTIF($A$3:$A$62,A26&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E26="","впишите, что предъявляем",IF(F26="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F26)),ISNUMBER(SEARCH(" и ",F26)),LOWER(F26)="все"),"ответственный — один человек",IF(G26="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
         <f>IF(AND(D26="пакет работ",ISNUMBER(G26)),G26*IF(LEFT(LOWER(H26),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n"/>
-      <c r="B27" s="15">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="14">
         <f>IF(A27="","",LEN(A27)-LEN(SUBSTITUTE(A27,".",""))+1)</f>
         <v/>
       </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="15">
-        <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$7:$A$66,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D27" s="14">
+        <f>IF(A27="","",IF(OR(B27=1,COUNTIF($A$3:$A$62,A27&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="15" t="n"/>
       <c r="J27" s="7">
-        <f>IF(A27="","",IF(COUNTIF($A$7:$A$66,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$7:$A$66,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
+        <f>IF(A27="","",IF(COUNTIF($A$3:$A$62,A27)&gt;1,"код повторяется",IF(C27="","нет названия",IF(D27="результат",IF(COUNTIF($A$3:$A$62,A27&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E27="","впишите, что предъявляем",IF(F27="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F27)),ISNUMBER(SEARCH(" и ",F27)),LOWER(F27)="все"),"ответственный — один человек",IF(G27="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
         <f>IF(AND(D27="пакет работ",ISNUMBER(G27)),G27*IF(LEFT(LOWER(H27),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="15">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="14">
         <f>IF(A28="","",LEN(A28)-LEN(SUBSTITUTE(A28,".",""))+1)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="15">
-        <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$7:$A$66,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D28" s="14">
+        <f>IF(A28="","",IF(OR(B28=1,COUNTIF($A$3:$A$62,A28&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="15" t="n"/>
       <c r="J28" s="7">
-        <f>IF(A28="","",IF(COUNTIF($A$7:$A$66,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$7:$A$66,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
+        <f>IF(A28="","",IF(COUNTIF($A$3:$A$62,A28)&gt;1,"код повторяется",IF(C28="","нет названия",IF(D28="результат",IF(COUNTIF($A$3:$A$62,A28&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E28="","впишите, что предъявляем",IF(F28="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F28)),ISNUMBER(SEARCH(" и ",F28)),LOWER(F28)="все"),"ответственный — один человек",IF(G28="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
         <f>IF(AND(D28="пакет работ",ISNUMBER(G28)),G28*IF(LEFT(LOWER(H28),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="15">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="14">
         <f>IF(A29="","",LEN(A29)-LEN(SUBSTITUTE(A29,".",""))+1)</f>
         <v/>
       </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="15">
-        <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$7:$A$66,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D29" s="14">
+        <f>IF(A29="","",IF(OR(B29=1,COUNTIF($A$3:$A$62,A29&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="15" t="n"/>
       <c r="J29" s="7">
-        <f>IF(A29="","",IF(COUNTIF($A$7:$A$66,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$7:$A$66,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
+        <f>IF(A29="","",IF(COUNTIF($A$3:$A$62,A29)&gt;1,"код повторяется",IF(C29="","нет названия",IF(D29="результат",IF(COUNTIF($A$3:$A$62,A29&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E29="","впишите, что предъявляем",IF(F29="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F29)),ISNUMBER(SEARCH(" и ",F29)),LOWER(F29)="все"),"ответственный — один человек",IF(G29="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
         <f>IF(AND(D29="пакет работ",ISNUMBER(G29)),G29*IF(LEFT(LOWER(H29),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="n"/>
-      <c r="B30" s="15">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="14">
         <f>IF(A30="","",LEN(A30)-LEN(SUBSTITUTE(A30,".",""))+1)</f>
         <v/>
       </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="15">
-        <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$7:$A$66,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D30" s="14">
+        <f>IF(A30="","",IF(OR(B30=1,COUNTIF($A$3:$A$62,A30&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="15" t="n"/>
       <c r="J30" s="7">
-        <f>IF(A30="","",IF(COUNTIF($A$7:$A$66,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$7:$A$66,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
+        <f>IF(A30="","",IF(COUNTIF($A$3:$A$62,A30)&gt;1,"код повторяется",IF(C30="","нет названия",IF(D30="результат",IF(COUNTIF($A$3:$A$62,A30&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E30="","впишите, что предъявляем",IF(F30="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F30)),ISNUMBER(SEARCH(" и ",F30)),LOWER(F30)="все"),"ответственный — один человек",IF(G30="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
         <f>IF(AND(D30="пакет работ",ISNUMBER(G30)),G30*IF(LEFT(LOWER(H30),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="n"/>
-      <c r="B31" s="15">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="14">
         <f>IF(A31="","",LEN(A31)-LEN(SUBSTITUTE(A31,".",""))+1)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="15">
-        <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$7:$A$66,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D31" s="14">
+        <f>IF(A31="","",IF(OR(B31=1,COUNTIF($A$3:$A$62,A31&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="15" t="n"/>
       <c r="J31" s="7">
-        <f>IF(A31="","",IF(COUNTIF($A$7:$A$66,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$7:$A$66,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
+        <f>IF(A31="","",IF(COUNTIF($A$3:$A$62,A31)&gt;1,"код повторяется",IF(C31="","нет названия",IF(D31="результат",IF(COUNTIF($A$3:$A$62,A31&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E31="","впишите, что предъявляем",IF(F31="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F31)),ISNUMBER(SEARCH(" и ",F31)),LOWER(F31)="все"),"ответственный — один человек",IF(G31="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
         <f>IF(AND(D31="пакет работ",ISNUMBER(G31)),G31*IF(LEFT(LOWER(H31),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="15">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="14">
         <f>IF(A32="","",LEN(A32)-LEN(SUBSTITUTE(A32,".",""))+1)</f>
         <v/>
       </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="15">
-        <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$7:$A$66,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D32" s="14">
+        <f>IF(A32="","",IF(OR(B32=1,COUNTIF($A$3:$A$62,A32&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="15" t="n"/>
       <c r="J32" s="7">
-        <f>IF(A32="","",IF(COUNTIF($A$7:$A$66,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$7:$A$66,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
+        <f>IF(A32="","",IF(COUNTIF($A$3:$A$62,A32)&gt;1,"код повторяется",IF(C32="","нет названия",IF(D32="результат",IF(COUNTIF($A$3:$A$62,A32&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E32="","впишите, что предъявляем",IF(F32="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F32)),ISNUMBER(SEARCH(" и ",F32)),LOWER(F32)="все"),"ответственный — один человек",IF(G32="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
         <f>IF(AND(D32="пакет работ",ISNUMBER(G32)),G32*IF(LEFT(LOWER(H32),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="n"/>
-      <c r="B33" s="15">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="14">
         <f>IF(A33="","",LEN(A33)-LEN(SUBSTITUTE(A33,".",""))+1)</f>
         <v/>
       </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="15">
-        <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$7:$A$66,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D33" s="14">
+        <f>IF(A33="","",IF(OR(B33=1,COUNTIF($A$3:$A$62,A33&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="15" t="n"/>
       <c r="J33" s="7">
-        <f>IF(A33="","",IF(COUNTIF($A$7:$A$66,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$7:$A$66,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
+        <f>IF(A33="","",IF(COUNTIF($A$3:$A$62,A33)&gt;1,"код повторяется",IF(C33="","нет названия",IF(D33="результат",IF(COUNTIF($A$3:$A$62,A33&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E33="","впишите, что предъявляем",IF(F33="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F33)),ISNUMBER(SEARCH(" и ",F33)),LOWER(F33)="все"),"ответственный — один человек",IF(G33="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K33" s="16">
         <f>IF(AND(D33="пакет работ",ISNUMBER(G33)),G33*IF(LEFT(LOWER(H33),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="15">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="14">
         <f>IF(A34="","",LEN(A34)-LEN(SUBSTITUTE(A34,".",""))+1)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="15">
-        <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$7:$A$66,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D34" s="14">
+        <f>IF(A34="","",IF(OR(B34=1,COUNTIF($A$3:$A$62,A34&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="15" t="n"/>
       <c r="J34" s="7">
-        <f>IF(A34="","",IF(COUNTIF($A$7:$A$66,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$7:$A$66,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K34" s="17">
+        <f>IF(A34="","",IF(COUNTIF($A$3:$A$62,A34)&gt;1,"код повторяется",IF(C34="","нет названия",IF(D34="результат",IF(COUNTIF($A$3:$A$62,A34&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E34="","впишите, что предъявляем",IF(F34="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F34)),ISNUMBER(SEARCH(" и ",F34)),LOWER(F34)="все"),"ответственный — один человек",IF(G34="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
         <f>IF(AND(D34="пакет работ",ISNUMBER(G34)),G34*IF(LEFT(LOWER(H34),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n"/>
-      <c r="B35" s="15">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="14">
         <f>IF(A35="","",LEN(A35)-LEN(SUBSTITUTE(A35,".",""))+1)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="15">
-        <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$7:$A$66,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D35" s="14">
+        <f>IF(A35="","",IF(OR(B35=1,COUNTIF($A$3:$A$62,A35&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="15" t="n"/>
       <c r="J35" s="7">
-        <f>IF(A35="","",IF(COUNTIF($A$7:$A$66,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$7:$A$66,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
+        <f>IF(A35="","",IF(COUNTIF($A$3:$A$62,A35)&gt;1,"код повторяется",IF(C35="","нет названия",IF(D35="результат",IF(COUNTIF($A$3:$A$62,A35&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E35="","впишите, что предъявляем",IF(F35="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F35)),ISNUMBER(SEARCH(" и ",F35)),LOWER(F35)="все"),"ответственный — один человек",IF(G35="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
         <f>IF(AND(D35="пакет работ",ISNUMBER(G35)),G35*IF(LEFT(LOWER(H35),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="15">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="14">
         <f>IF(A36="","",LEN(A36)-LEN(SUBSTITUTE(A36,".",""))+1)</f>
         <v/>
       </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="15">
-        <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$7:$A$66,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D36" s="14">
+        <f>IF(A36="","",IF(OR(B36=1,COUNTIF($A$3:$A$62,A36&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="15" t="n"/>
       <c r="J36" s="7">
-        <f>IF(A36="","",IF(COUNTIF($A$7:$A$66,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$7:$A$66,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
+        <f>IF(A36="","",IF(COUNTIF($A$3:$A$62,A36)&gt;1,"код повторяется",IF(C36="","нет названия",IF(D36="результат",IF(COUNTIF($A$3:$A$62,A36&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E36="","впишите, что предъявляем",IF(F36="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F36)),ISNUMBER(SEARCH(" и ",F36)),LOWER(F36)="все"),"ответственный — один человек",IF(G36="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
         <f>IF(AND(D36="пакет работ",ISNUMBER(G36)),G36*IF(LEFT(LOWER(H36),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="15">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="14">
         <f>IF(A37="","",LEN(A37)-LEN(SUBSTITUTE(A37,".",""))+1)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="15">
-        <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$7:$A$66,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D37" s="14">
+        <f>IF(A37="","",IF(OR(B37=1,COUNTIF($A$3:$A$62,A37&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="15" t="n"/>
       <c r="J37" s="7">
-        <f>IF(A37="","",IF(COUNTIF($A$7:$A$66,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$7:$A$66,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
+        <f>IF(A37="","",IF(COUNTIF($A$3:$A$62,A37)&gt;1,"код повторяется",IF(C37="","нет названия",IF(D37="результат",IF(COUNTIF($A$3:$A$62,A37&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E37="","впишите, что предъявляем",IF(F37="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F37)),ISNUMBER(SEARCH(" и ",F37)),LOWER(F37)="все"),"ответственный — один человек",IF(G37="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
         <f>IF(AND(D37="пакет работ",ISNUMBER(G37)),G37*IF(LEFT(LOWER(H37),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="15">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="14">
         <f>IF(A38="","",LEN(A38)-LEN(SUBSTITUTE(A38,".",""))+1)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="15">
-        <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$7:$A$66,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D38" s="14">
+        <f>IF(A38="","",IF(OR(B38=1,COUNTIF($A$3:$A$62,A38&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="15" t="n"/>
       <c r="J38" s="7">
-        <f>IF(A38="","",IF(COUNTIF($A$7:$A$66,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$7:$A$66,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K38" s="17">
+        <f>IF(A38="","",IF(COUNTIF($A$3:$A$62,A38)&gt;1,"код повторяется",IF(C38="","нет названия",IF(D38="результат",IF(COUNTIF($A$3:$A$62,A38&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E38="","впишите, что предъявляем",IF(F38="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F38)),ISNUMBER(SEARCH(" и ",F38)),LOWER(F38)="все"),"ответственный — один человек",IF(G38="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K38" s="16">
         <f>IF(AND(D38="пакет работ",ISNUMBER(G38)),G38*IF(LEFT(LOWER(H38),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="15">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="14">
         <f>IF(A39="","",LEN(A39)-LEN(SUBSTITUTE(A39,".",""))+1)</f>
         <v/>
       </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="15">
-        <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$7:$A$66,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D39" s="14">
+        <f>IF(A39="","",IF(OR(B39=1,COUNTIF($A$3:$A$62,A39&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="15" t="n"/>
       <c r="J39" s="7">
-        <f>IF(A39="","",IF(COUNTIF($A$7:$A$66,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$7:$A$66,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K39" s="17">
+        <f>IF(A39="","",IF(COUNTIF($A$3:$A$62,A39)&gt;1,"код повторяется",IF(C39="","нет названия",IF(D39="результат",IF(COUNTIF($A$3:$A$62,A39&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E39="","впишите, что предъявляем",IF(F39="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F39)),ISNUMBER(SEARCH(" и ",F39)),LOWER(F39)="все"),"ответственный — один человек",IF(G39="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K39" s="16">
         <f>IF(AND(D39="пакет работ",ISNUMBER(G39)),G39*IF(LEFT(LOWER(H39),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="15">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="14">
         <f>IF(A40="","",LEN(A40)-LEN(SUBSTITUTE(A40,".",""))+1)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="15">
-        <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$7:$A$66,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D40" s="14">
+        <f>IF(A40="","",IF(OR(B40=1,COUNTIF($A$3:$A$62,A40&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="15" t="n"/>
       <c r="J40" s="7">
-        <f>IF(A40="","",IF(COUNTIF($A$7:$A$66,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$7:$A$66,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K40" s="17">
+        <f>IF(A40="","",IF(COUNTIF($A$3:$A$62,A40)&gt;1,"код повторяется",IF(C40="","нет названия",IF(D40="результат",IF(COUNTIF($A$3:$A$62,A40&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E40="","впишите, что предъявляем",IF(F40="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F40)),ISNUMBER(SEARCH(" и ",F40)),LOWER(F40)="все"),"ответственный — один человек",IF(G40="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
         <f>IF(AND(D40="пакет работ",ISNUMBER(G40)),G40*IF(LEFT(LOWER(H40),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="15">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="14">
         <f>IF(A41="","",LEN(A41)-LEN(SUBSTITUTE(A41,".",""))+1)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="15">
-        <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$7:$A$66,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D41" s="14">
+        <f>IF(A41="","",IF(OR(B41=1,COUNTIF($A$3:$A$62,A41&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="15" t="n"/>
       <c r="J41" s="7">
-        <f>IF(A41="","",IF(COUNTIF($A$7:$A$66,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$7:$A$66,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K41" s="17">
+        <f>IF(A41="","",IF(COUNTIF($A$3:$A$62,A41)&gt;1,"код повторяется",IF(C41="","нет названия",IF(D41="результат",IF(COUNTIF($A$3:$A$62,A41&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E41="","впишите, что предъявляем",IF(F41="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F41)),ISNUMBER(SEARCH(" и ",F41)),LOWER(F41)="все"),"ответственный — один человек",IF(G41="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K41" s="16">
         <f>IF(AND(D41="пакет работ",ISNUMBER(G41)),G41*IF(LEFT(LOWER(H41),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="15">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="14">
         <f>IF(A42="","",LEN(A42)-LEN(SUBSTITUTE(A42,".",""))+1)</f>
         <v/>
       </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="15">
-        <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$7:$A$66,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D42" s="14">
+        <f>IF(A42="","",IF(OR(B42=1,COUNTIF($A$3:$A$62,A42&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="15" t="n"/>
       <c r="J42" s="7">
-        <f>IF(A42="","",IF(COUNTIF($A$7:$A$66,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$7:$A$66,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K42" s="17">
+        <f>IF(A42="","",IF(COUNTIF($A$3:$A$62,A42)&gt;1,"код повторяется",IF(C42="","нет названия",IF(D42="результат",IF(COUNTIF($A$3:$A$62,A42&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E42="","впишите, что предъявляем",IF(F42="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F42)),ISNUMBER(SEARCH(" и ",F42)),LOWER(F42)="все"),"ответственный — один человек",IF(G42="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K42" s="16">
         <f>IF(AND(D42="пакет работ",ISNUMBER(G42)),G42*IF(LEFT(LOWER(H42),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="15">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="14">
         <f>IF(A43="","",LEN(A43)-LEN(SUBSTITUTE(A43,".",""))+1)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="15">
-        <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$7:$A$66,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D43" s="14">
+        <f>IF(A43="","",IF(OR(B43=1,COUNTIF($A$3:$A$62,A43&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="15" t="n"/>
       <c r="J43" s="7">
-        <f>IF(A43="","",IF(COUNTIF($A$7:$A$66,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$7:$A$66,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K43" s="17">
+        <f>IF(A43="","",IF(COUNTIF($A$3:$A$62,A43)&gt;1,"код повторяется",IF(C43="","нет названия",IF(D43="результат",IF(COUNTIF($A$3:$A$62,A43&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E43="","впишите, что предъявляем",IF(F43="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F43)),ISNUMBER(SEARCH(" и ",F43)),LOWER(F43)="все"),"ответственный — один человек",IF(G43="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K43" s="16">
         <f>IF(AND(D43="пакет работ",ISNUMBER(G43)),G43*IF(LEFT(LOWER(H43),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="n"/>
-      <c r="B44" s="15">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="14">
         <f>IF(A44="","",LEN(A44)-LEN(SUBSTITUTE(A44,".",""))+1)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="15">
-        <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$7:$A$66,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D44" s="14">
+        <f>IF(A44="","",IF(OR(B44=1,COUNTIF($A$3:$A$62,A44&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="7">
-        <f>IF(A44="","",IF(COUNTIF($A$7:$A$66,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$7:$A$66,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K44" s="17">
+        <f>IF(A44="","",IF(COUNTIF($A$3:$A$62,A44)&gt;1,"код повторяется",IF(C44="","нет названия",IF(D44="результат",IF(COUNTIF($A$3:$A$62,A44&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E44="","впишите, что предъявляем",IF(F44="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F44)),ISNUMBER(SEARCH(" и ",F44)),LOWER(F44)="все"),"ответственный — один человек",IF(G44="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K44" s="16">
         <f>IF(AND(D44="пакет работ",ISNUMBER(G44)),G44*IF(LEFT(LOWER(H44),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="15">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="14">
         <f>IF(A45="","",LEN(A45)-LEN(SUBSTITUTE(A45,".",""))+1)</f>
         <v/>
       </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="15">
-        <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$7:$A$66,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D45" s="14">
+        <f>IF(A45="","",IF(OR(B45=1,COUNTIF($A$3:$A$62,A45&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="15" t="n"/>
       <c r="J45" s="7">
-        <f>IF(A45="","",IF(COUNTIF($A$7:$A$66,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$7:$A$66,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K45" s="17">
+        <f>IF(A45="","",IF(COUNTIF($A$3:$A$62,A45)&gt;1,"код повторяется",IF(C45="","нет названия",IF(D45="результат",IF(COUNTIF($A$3:$A$62,A45&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E45="","впишите, что предъявляем",IF(F45="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F45)),ISNUMBER(SEARCH(" и ",F45)),LOWER(F45)="все"),"ответственный — один человек",IF(G45="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K45" s="16">
         <f>IF(AND(D45="пакет работ",ISNUMBER(G45)),G45*IF(LEFT(LOWER(H45),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="n"/>
-      <c r="B46" s="15">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="14">
         <f>IF(A46="","",LEN(A46)-LEN(SUBSTITUTE(A46,".",""))+1)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="15">
-        <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$7:$A$66,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D46" s="14">
+        <f>IF(A46="","",IF(OR(B46=1,COUNTIF($A$3:$A$62,A46&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="7">
-        <f>IF(A46="","",IF(COUNTIF($A$7:$A$66,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$7:$A$66,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K46" s="17">
+        <f>IF(A46="","",IF(COUNTIF($A$3:$A$62,A46)&gt;1,"код повторяется",IF(C46="","нет названия",IF(D46="результат",IF(COUNTIF($A$3:$A$62,A46&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E46="","впишите, что предъявляем",IF(F46="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F46)),ISNUMBER(SEARCH(" и ",F46)),LOWER(F46)="все"),"ответственный — один человек",IF(G46="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K46" s="16">
         <f>IF(AND(D46="пакет работ",ISNUMBER(G46)),G46*IF(LEFT(LOWER(H46),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="14">
         <f>IF(A47="","",LEN(A47)-LEN(SUBSTITUTE(A47,".",""))+1)</f>
         <v/>
       </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="15">
-        <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$7:$A$66,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D47" s="14">
+        <f>IF(A47="","",IF(OR(B47=1,COUNTIF($A$3:$A$62,A47&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="15" t="n"/>
       <c r="J47" s="7">
-        <f>IF(A47="","",IF(COUNTIF($A$7:$A$66,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$7:$A$66,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K47" s="17">
+        <f>IF(A47="","",IF(COUNTIF($A$3:$A$62,A47)&gt;1,"код повторяется",IF(C47="","нет названия",IF(D47="результат",IF(COUNTIF($A$3:$A$62,A47&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E47="","впишите, что предъявляем",IF(F47="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F47)),ISNUMBER(SEARCH(" и ",F47)),LOWER(F47)="все"),"ответственный — один человек",IF(G47="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K47" s="16">
         <f>IF(AND(D47="пакет работ",ISNUMBER(G47)),G47*IF(LEFT(LOWER(H47),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="n"/>
-      <c r="B48" s="15">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="14">
         <f>IF(A48="","",LEN(A48)-LEN(SUBSTITUTE(A48,".",""))+1)</f>
         <v/>
       </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="15">
-        <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$7:$A$66,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D48" s="14">
+        <f>IF(A48="","",IF(OR(B48=1,COUNTIF($A$3:$A$62,A48&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="15" t="n"/>
       <c r="J48" s="7">
-        <f>IF(A48="","",IF(COUNTIF($A$7:$A$66,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$7:$A$66,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K48" s="17">
+        <f>IF(A48="","",IF(COUNTIF($A$3:$A$62,A48)&gt;1,"код повторяется",IF(C48="","нет названия",IF(D48="результат",IF(COUNTIF($A$3:$A$62,A48&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E48="","впишите, что предъявляем",IF(F48="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F48)),ISNUMBER(SEARCH(" и ",F48)),LOWER(F48)="все"),"ответственный — один человек",IF(G48="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K48" s="16">
         <f>IF(AND(D48="пакет работ",ISNUMBER(G48)),G48*IF(LEFT(LOWER(H48),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="n"/>
-      <c r="B49" s="15">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="14">
         <f>IF(A49="","",LEN(A49)-LEN(SUBSTITUTE(A49,".",""))+1)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="15">
-        <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$7:$A$66,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D49" s="14">
+        <f>IF(A49="","",IF(OR(B49=1,COUNTIF($A$3:$A$62,A49&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="15" t="n"/>
       <c r="J49" s="7">
-        <f>IF(A49="","",IF(COUNTIF($A$7:$A$66,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$7:$A$66,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K49" s="17">
+        <f>IF(A49="","",IF(COUNTIF($A$3:$A$62,A49)&gt;1,"код повторяется",IF(C49="","нет названия",IF(D49="результат",IF(COUNTIF($A$3:$A$62,A49&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E49="","впишите, что предъявляем",IF(F49="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F49)),ISNUMBER(SEARCH(" и ",F49)),LOWER(F49)="все"),"ответственный — один человек",IF(G49="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K49" s="16">
         <f>IF(AND(D49="пакет работ",ISNUMBER(G49)),G49*IF(LEFT(LOWER(H49),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n"/>
-      <c r="B50" s="15">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="14">
         <f>IF(A50="","",LEN(A50)-LEN(SUBSTITUTE(A50,".",""))+1)</f>
         <v/>
       </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="15">
-        <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$7:$A$66,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D50" s="14">
+        <f>IF(A50="","",IF(OR(B50=1,COUNTIF($A$3:$A$62,A50&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="15" t="n"/>
       <c r="J50" s="7">
-        <f>IF(A50="","",IF(COUNTIF($A$7:$A$66,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$7:$A$66,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K50" s="17">
+        <f>IF(A50="","",IF(COUNTIF($A$3:$A$62,A50)&gt;1,"код повторяется",IF(C50="","нет названия",IF(D50="результат",IF(COUNTIF($A$3:$A$62,A50&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E50="","впишите, что предъявляем",IF(F50="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F50)),ISNUMBER(SEARCH(" и ",F50)),LOWER(F50)="все"),"ответственный — один человек",IF(G50="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K50" s="16">
         <f>IF(AND(D50="пакет работ",ISNUMBER(G50)),G50*IF(LEFT(LOWER(H50),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="15">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="14">
         <f>IF(A51="","",LEN(A51)-LEN(SUBSTITUTE(A51,".",""))+1)</f>
         <v/>
       </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="15">
-        <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$7:$A$66,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D51" s="14">
+        <f>IF(A51="","",IF(OR(B51=1,COUNTIF($A$3:$A$62,A51&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="15" t="n"/>
       <c r="J51" s="7">
-        <f>IF(A51="","",IF(COUNTIF($A$7:$A$66,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$7:$A$66,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K51" s="17">
+        <f>IF(A51="","",IF(COUNTIF($A$3:$A$62,A51)&gt;1,"код повторяется",IF(C51="","нет названия",IF(D51="результат",IF(COUNTIF($A$3:$A$62,A51&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E51="","впишите, что предъявляем",IF(F51="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F51)),ISNUMBER(SEARCH(" и ",F51)),LOWER(F51)="все"),"ответственный — один человек",IF(G51="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K51" s="16">
         <f>IF(AND(D51="пакет работ",ISNUMBER(G51)),G51*IF(LEFT(LOWER(H51),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="n"/>
-      <c r="B52" s="15">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="14">
         <f>IF(A52="","",LEN(A52)-LEN(SUBSTITUTE(A52,".",""))+1)</f>
         <v/>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="15">
-        <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$7:$A$66,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D52" s="14">
+        <f>IF(A52="","",IF(OR(B52=1,COUNTIF($A$3:$A$62,A52&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="15" t="n"/>
       <c r="J52" s="7">
-        <f>IF(A52="","",IF(COUNTIF($A$7:$A$66,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$7:$A$66,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K52" s="17">
+        <f>IF(A52="","",IF(COUNTIF($A$3:$A$62,A52)&gt;1,"код повторяется",IF(C52="","нет названия",IF(D52="результат",IF(COUNTIF($A$3:$A$62,A52&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E52="","впишите, что предъявляем",IF(F52="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F52)),ISNUMBER(SEARCH(" и ",F52)),LOWER(F52)="все"),"ответственный — один человек",IF(G52="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K52" s="16">
         <f>IF(AND(D52="пакет работ",ISNUMBER(G52)),G52*IF(LEFT(LOWER(H52),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="15">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="14">
         <f>IF(A53="","",LEN(A53)-LEN(SUBSTITUTE(A53,".",""))+1)</f>
         <v/>
       </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="15">
-        <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$7:$A$66,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D53" s="14">
+        <f>IF(A53="","",IF(OR(B53=1,COUNTIF($A$3:$A$62,A53&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="15" t="n"/>
       <c r="J53" s="7">
-        <f>IF(A53="","",IF(COUNTIF($A$7:$A$66,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$7:$A$66,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K53" s="17">
+        <f>IF(A53="","",IF(COUNTIF($A$3:$A$62,A53)&gt;1,"код повторяется",IF(C53="","нет названия",IF(D53="результат",IF(COUNTIF($A$3:$A$62,A53&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E53="","впишите, что предъявляем",IF(F53="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F53)),ISNUMBER(SEARCH(" и ",F53)),LOWER(F53)="все"),"ответственный — один человек",IF(G53="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K53" s="16">
         <f>IF(AND(D53="пакет работ",ISNUMBER(G53)),G53*IF(LEFT(LOWER(H53),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="15">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="14">
         <f>IF(A54="","",LEN(A54)-LEN(SUBSTITUTE(A54,".",""))+1)</f>
         <v/>
       </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="15">
-        <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$7:$A$66,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D54" s="14">
+        <f>IF(A54="","",IF(OR(B54=1,COUNTIF($A$3:$A$62,A54&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="15" t="n"/>
       <c r="J54" s="7">
-        <f>IF(A54="","",IF(COUNTIF($A$7:$A$66,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$7:$A$66,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K54" s="17">
+        <f>IF(A54="","",IF(COUNTIF($A$3:$A$62,A54)&gt;1,"код повторяется",IF(C54="","нет названия",IF(D54="результат",IF(COUNTIF($A$3:$A$62,A54&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E54="","впишите, что предъявляем",IF(F54="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F54)),ISNUMBER(SEARCH(" и ",F54)),LOWER(F54)="все"),"ответственный — один человек",IF(G54="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K54" s="16">
         <f>IF(AND(D54="пакет работ",ISNUMBER(G54)),G54*IF(LEFT(LOWER(H54),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="15">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="14">
         <f>IF(A55="","",LEN(A55)-LEN(SUBSTITUTE(A55,".",""))+1)</f>
         <v/>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="15">
-        <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$7:$A$66,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D55" s="14">
+        <f>IF(A55="","",IF(OR(B55=1,COUNTIF($A$3:$A$62,A55&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="15" t="n"/>
       <c r="J55" s="7">
-        <f>IF(A55="","",IF(COUNTIF($A$7:$A$66,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$7:$A$66,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K55" s="17">
+        <f>IF(A55="","",IF(COUNTIF($A$3:$A$62,A55)&gt;1,"код повторяется",IF(C55="","нет названия",IF(D55="результат",IF(COUNTIF($A$3:$A$62,A55&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E55="","впишите, что предъявляем",IF(F55="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F55)),ISNUMBER(SEARCH(" и ",F55)),LOWER(F55)="все"),"ответственный — один человек",IF(G55="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K55" s="16">
         <f>IF(AND(D55="пакет работ",ISNUMBER(G55)),G55*IF(LEFT(LOWER(H55),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="15">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="14">
         <f>IF(A56="","",LEN(A56)-LEN(SUBSTITUTE(A56,".",""))+1)</f>
         <v/>
       </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="15">
-        <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$7:$A$66,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D56" s="14">
+        <f>IF(A56="","",IF(OR(B56=1,COUNTIF($A$3:$A$62,A56&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="15" t="n"/>
       <c r="J56" s="7">
-        <f>IF(A56="","",IF(COUNTIF($A$7:$A$66,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$7:$A$66,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K56" s="17">
+        <f>IF(A56="","",IF(COUNTIF($A$3:$A$62,A56)&gt;1,"код повторяется",IF(C56="","нет названия",IF(D56="результат",IF(COUNTIF($A$3:$A$62,A56&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E56="","впишите, что предъявляем",IF(F56="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F56)),ISNUMBER(SEARCH(" и ",F56)),LOWER(F56)="все"),"ответственный — один человек",IF(G56="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K56" s="16">
         <f>IF(AND(D56="пакет работ",ISNUMBER(G56)),G56*IF(LEFT(LOWER(H56),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="n"/>
-      <c r="B57" s="15">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="14">
         <f>IF(A57="","",LEN(A57)-LEN(SUBSTITUTE(A57,".",""))+1)</f>
         <v/>
       </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="15">
-        <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$7:$A$66,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D57" s="14">
+        <f>IF(A57="","",IF(OR(B57=1,COUNTIF($A$3:$A$62,A57&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="15" t="n"/>
       <c r="J57" s="7">
-        <f>IF(A57="","",IF(COUNTIF($A$7:$A$66,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$7:$A$66,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K57" s="17">
+        <f>IF(A57="","",IF(COUNTIF($A$3:$A$62,A57)&gt;1,"код повторяется",IF(C57="","нет названия",IF(D57="результат",IF(COUNTIF($A$3:$A$62,A57&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E57="","впишите, что предъявляем",IF(F57="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F57)),ISNUMBER(SEARCH(" и ",F57)),LOWER(F57)="все"),"ответственный — один человек",IF(G57="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K57" s="16">
         <f>IF(AND(D57="пакет работ",ISNUMBER(G57)),G57*IF(LEFT(LOWER(H57),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="n"/>
-      <c r="B58" s="15">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="14">
         <f>IF(A58="","",LEN(A58)-LEN(SUBSTITUTE(A58,".",""))+1)</f>
         <v/>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="15">
-        <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$7:$A$66,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D58" s="14">
+        <f>IF(A58="","",IF(OR(B58=1,COUNTIF($A$3:$A$62,A58&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="15" t="n"/>
       <c r="J58" s="7">
-        <f>IF(A58="","",IF(COUNTIF($A$7:$A$66,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$7:$A$66,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K58" s="17">
+        <f>IF(A58="","",IF(COUNTIF($A$3:$A$62,A58)&gt;1,"код повторяется",IF(C58="","нет названия",IF(D58="результат",IF(COUNTIF($A$3:$A$62,A58&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E58="","впишите, что предъявляем",IF(F58="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F58)),ISNUMBER(SEARCH(" и ",F58)),LOWER(F58)="все"),"ответственный — один человек",IF(G58="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K58" s="16">
         <f>IF(AND(D58="пакет работ",ISNUMBER(G58)),G58*IF(LEFT(LOWER(H58),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="15">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="14">
         <f>IF(A59="","",LEN(A59)-LEN(SUBSTITUTE(A59,".",""))+1)</f>
         <v/>
       </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="15">
-        <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$7:$A$66,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D59" s="14">
+        <f>IF(A59="","",IF(OR(B59=1,COUNTIF($A$3:$A$62,A59&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="15" t="n"/>
       <c r="J59" s="7">
-        <f>IF(A59="","",IF(COUNTIF($A$7:$A$66,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$7:$A$66,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K59" s="17">
+        <f>IF(A59="","",IF(COUNTIF($A$3:$A$62,A59)&gt;1,"код повторяется",IF(C59="","нет названия",IF(D59="результат",IF(COUNTIF($A$3:$A$62,A59&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E59="","впишите, что предъявляем",IF(F59="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F59)),ISNUMBER(SEARCH(" и ",F59)),LOWER(F59)="все"),"ответственный — один человек",IF(G59="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K59" s="16">
         <f>IF(AND(D59="пакет работ",ISNUMBER(G59)),G59*IF(LEFT(LOWER(H59),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="n"/>
-      <c r="B60" s="15">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="14">
         <f>IF(A60="","",LEN(A60)-LEN(SUBSTITUTE(A60,".",""))+1)</f>
         <v/>
       </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="15">
-        <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$7:$A$66,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D60" s="14">
+        <f>IF(A60="","",IF(OR(B60=1,COUNTIF($A$3:$A$62,A60&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="15" t="n"/>
       <c r="J60" s="7">
-        <f>IF(A60="","",IF(COUNTIF($A$7:$A$66,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$7:$A$66,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K60" s="17">
+        <f>IF(A60="","",IF(COUNTIF($A$3:$A$62,A60)&gt;1,"код повторяется",IF(C60="","нет названия",IF(D60="результат",IF(COUNTIF($A$3:$A$62,A60&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E60="","впишите, что предъявляем",IF(F60="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F60)),ISNUMBER(SEARCH(" и ",F60)),LOWER(F60)="все"),"ответственный — один человек",IF(G60="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K60" s="16">
         <f>IF(AND(D60="пакет работ",ISNUMBER(G60)),G60*IF(LEFT(LOWER(H60),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="n"/>
-      <c r="B61" s="15">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="14">
         <f>IF(A61="","",LEN(A61)-LEN(SUBSTITUTE(A61,".",""))+1)</f>
         <v/>
       </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="15">
-        <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$7:$A$66,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D61" s="14">
+        <f>IF(A61="","",IF(OR(B61=1,COUNTIF($A$3:$A$62,A61&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="15" t="n"/>
       <c r="J61" s="7">
-        <f>IF(A61="","",IF(COUNTIF($A$7:$A$66,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$7:$A$66,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K61" s="17">
+        <f>IF(A61="","",IF(COUNTIF($A$3:$A$62,A61)&gt;1,"код повторяется",IF(C61="","нет названия",IF(D61="результат",IF(COUNTIF($A$3:$A$62,A61&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E61="","впишите, что предъявляем",IF(F61="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F61)),ISNUMBER(SEARCH(" и ",F61)),LOWER(F61)="все"),"ответственный — один человек",IF(G61="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K61" s="16">
         <f>IF(AND(D61="пакет работ",ISNUMBER(G61)),G61*IF(LEFT(LOWER(H61),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="n"/>
-      <c r="B62" s="15">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="14">
         <f>IF(A62="","",LEN(A62)-LEN(SUBSTITUTE(A62,".",""))+1)</f>
         <v/>
       </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="15">
-        <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$7:$A$66,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
+      <c r="D62" s="14">
+        <f>IF(A62="","",IF(OR(B62=1,COUNTIF($A$3:$A$62,A62&amp;".*")&gt;0),"результат","пакет работ"))</f>
         <v/>
       </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="15" t="n"/>
       <c r="J62" s="7">
-        <f>IF(A62="","",IF(COUNTIF($A$7:$A$66,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$7:$A$66,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K62" s="17">
+        <f>IF(A62="","",IF(COUNTIF($A$3:$A$62,A62)&gt;1,"код повторяется",IF(C62="","нет названия",IF(D62="результат",IF(COUNTIF($A$3:$A$62,A62&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E62="","впишите, что предъявляем",IF(F62="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F62)),ISNUMBER(SEARCH(" и ",F62)),LOWER(F62)="все"),"ответственный — один человек",IF(G62="","оцените длительность","✓"))))))))</f>
+        <v/>
+      </c>
+      <c r="K62" s="16">
         <f>IF(AND(D62="пакет работ",ISNUMBER(G62)),G62*IF(LEFT(LOWER(H62),1)="д",1/7,1),0)</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="n"/>
-      <c r="B63" s="15">
-        <f>IF(A63="","",LEN(A63)-LEN(SUBSTITUTE(A63,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="15">
-        <f>IF(A63="","",IF(OR(B63=1,COUNTIF($A$7:$A$66,A63&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="16" t="n"/>
-      <c r="J63" s="7">
-        <f>IF(A63="","",IF(COUNTIF($A$7:$A$66,A63)&gt;1,"код повторяется",IF(C63="","нет названия",IF(D63="результат",IF(COUNTIF($A$7:$A$66,A63&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E63="","впишите, что предъявляем",IF(F63="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F63)),ISNUMBER(SEARCH(" и ",F63)),LOWER(F63)="все"),"ответственный — один человек",IF(G63="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K63" s="17">
-        <f>IF(AND(D63="пакет работ",ISNUMBER(G63)),G63*IF(LEFT(LOWER(H63),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="n"/>
-      <c r="B64" s="15">
-        <f>IF(A64="","",LEN(A64)-LEN(SUBSTITUTE(A64,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="15">
-        <f>IF(A64="","",IF(OR(B64=1,COUNTIF($A$7:$A$66,A64&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="7">
-        <f>IF(A64="","",IF(COUNTIF($A$7:$A$66,A64)&gt;1,"код повторяется",IF(C64="","нет названия",IF(D64="результат",IF(COUNTIF($A$7:$A$66,A64&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E64="","впишите, что предъявляем",IF(F64="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F64)),ISNUMBER(SEARCH(" и ",F64)),LOWER(F64)="все"),"ответственный — один человек",IF(G64="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K64" s="17">
-        <f>IF(AND(D64="пакет работ",ISNUMBER(G64)),G64*IF(LEFT(LOWER(H64),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="n"/>
-      <c r="B65" s="15">
-        <f>IF(A65="","",LEN(A65)-LEN(SUBSTITUTE(A65,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="15">
-        <f>IF(A65="","",IF(OR(B65=1,COUNTIF($A$7:$A$66,A65&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="16" t="n"/>
-      <c r="J65" s="7">
-        <f>IF(A65="","",IF(COUNTIF($A$7:$A$66,A65)&gt;1,"код повторяется",IF(C65="","нет названия",IF(D65="результат",IF(COUNTIF($A$7:$A$66,A65&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E65="","впишите, что предъявляем",IF(F65="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F65)),ISNUMBER(SEARCH(" и ",F65)),LOWER(F65)="все"),"ответственный — один человек",IF(G65="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K65" s="17">
-        <f>IF(AND(D65="пакет работ",ISNUMBER(G65)),G65*IF(LEFT(LOWER(H65),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="n"/>
-      <c r="B66" s="15">
-        <f>IF(A66="","",LEN(A66)-LEN(SUBSTITUTE(A66,".",""))+1)</f>
-        <v/>
-      </c>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="15">
-        <f>IF(A66="","",IF(OR(B66=1,COUNTIF($A$7:$A$66,A66&amp;".*")&gt;0),"результат","пакет работ"))</f>
-        <v/>
-      </c>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="7">
-        <f>IF(A66="","",IF(COUNTIF($A$7:$A$66,A66)&gt;1,"код повторяется",IF(C66="","нет названия",IF(D66="результат",IF(COUNTIF($A$7:$A$66,A66&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E66="","впишите, что предъявляем",IF(F66="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F66)),ISNUMBER(SEARCH(" и ",F66)),LOWER(F66)="все"),"ответственный — один человек",IF(G66="","оцените длительность","✓"))))))))</f>
-        <v/>
-      </c>
-      <c r="K66" s="17">
-        <f>IF(AND(D66="пакет работ",ISNUMBER(G66)),G66*IF(LEFT(LOWER(H66),1)="д",1/7,1),0)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+  <mergeCells count="2">
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:J66">
+  <conditionalFormatting sqref="F1">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$D7="результат"</formula>
+      <formula>OR(ISNUMBER(SEARCH("добавьте",$F$1)),COUNTIF($J$3:$J$62,"?*")-COUNTIF($J$3:$J$62,"✓")&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J66">
+  <conditionalFormatting sqref="A3:J62">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(J7&lt;&gt;"",J7&lt;&gt;"✓")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>J7="✓"</formula>
+      <formula>$D3="результат"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E4="добавьте"</formula>
+  <conditionalFormatting sqref="J3:J62">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(J3&lt;&gt;"",J3&lt;&gt;"✓")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>F4="добавьте"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>D4&gt;0</formula>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>J3="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H7:H66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
+    <dataValidation sqref="H3:H62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Единица" error="Выберите из списка: недель или дней." type="list" errorStyle="stop">
       <formula1>"недель,дней"</formula1>
     </dataValidation>
   </dataValidations>

--- a/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
+++ b/zanyatiya/Zanyatie_06_WBS_Tablica.xlsx
@@ -186,7 +186,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -292,6 +292,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Курс ОПД</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Какие пакеты должны закончиться, прежде чем этот можно начать. Пример: у пакета «2.1 Калибровка» — «1.2»: калибровать можно только собранную схему. Пусто — можно начинать сразу. У крупных результатов не заполняется. Нужно для диаграммы Ганта на следующей паре.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Курс ОПД</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Какие пакеты должны закончиться, прежде чем этот можно начать. Пример: у пакета «2.1 Калибровка» — «1.2»: калибровать можно только собранную схему. Пусто — можно начинать сразу. У крупных результатов не заполняется. Нужно для диаграммы Ганта на следующей паре.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,7 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Таблица повторяет оборот бланка WBS. Можно работать на бумаге, можно здесь — на следующую пару принесите лист или откройте файл: из пакетов будем строить диаграмму Ганта.</t>
@@ -611,7 +641,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>1. Лист «Команда»: впишите участников и выберите роли. В списке «Роли команды» справа — четыре роли с первого занятия; если команда придумала свои роли, впишите их в пустые строки этого списка — они появятся в выпадающем меню.</t>
@@ -625,38 +655,38 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>3. Крупные результаты — коды 1, 2, 3… Возьмите выбранные ветви дерева целей. Добавьте «Отчёт и защита» и «Управление проектом»: эту работу всё равно придётся сделать.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>4. Пакеты работ — коды 1.1, 1.2, 2.1… Каждый пакет пишите строкой сразу под своим результатом. Называйте существительным: «протокол испытаний», а не «испытать».</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>5. Для каждого пакета: что предъявляем, один ответственный (из списка), длительность и единица — недель или дней.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>6. Уровень, тип и столбец «Проверка» заполняются сами. Красное — что ещё поправить, зелёная галочка — готово.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="80" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7. «Зависит от» оставьте пустым — заполним на следующей паре.</t>
+          <t>7. «Зависит от» — какие пакеты должны закончиться, прежде чем этот можно начать. Впишите их коды через запятую: «1.1, 1.2». Пусто — пакет можно начинать сразу. У крупных результатов столбец не заполняется. Это уже не сама WBS, а подготовка к диаграмме Ганта: на следующей паре по этим связям найдём цепочку пакетов, которая задаёт срок всего проекта. Если связи пока непонятны, оставьте пустым — разберём на паре. Образец — на листе «Пример — умный горшок».</t>
         </is>
       </c>
     </row>
@@ -702,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Пакет делается одним человеком за срок от нескольких вечеров до двух недель. Больше — дробите, меньше часа — объедините с соседним.</t>
@@ -716,10 +746,10 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Дат и порядка работ в WBS нет: WBS отвечает на вопрос «что», календарный план — «когда».</t>
+          <t>В самой WBS дат и порядка работ нет: она отвечает на вопрос «что». Порядок появляется в столбце «Зависит от», сроки — в диаграмме Ганта.</t>
         </is>
       </c>
     </row>
@@ -998,7 +1028,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Зависит от (коды) — на следующей паре</t>
+          <t>Зависит от: коды пакетов через запятую</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -2546,6 +2576,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2631,7 +2662,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Зависит от (коды) — на следующей паре</t>
+          <t>Зависит от: коды пакетов через запятую</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -2762,7 +2793,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I5" s="15" t="n"/>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J5" s="7">
         <f>IF(A5="","",IF(COUNTIF($A$3:$A$62,A5)&gt;1,"код повторяется",IF(C5="","нет названия",IF(D5="результат",IF(COUNTIF($A$3:$A$62,A5&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E5="","впишите, что предъявляем",IF(F5="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F5)),ISNUMBER(SEARCH(" и ",F5)),LOWER(F5)="все"),"ответственный — один человек",IF(G5="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -2809,7 +2844,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I6" s="15" t="n"/>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="J6" s="7">
         <f>IF(A6="","",IF(COUNTIF($A$3:$A$62,A6)&gt;1,"код повторяется",IF(C6="","нет названия",IF(D6="результат",IF(COUNTIF($A$3:$A$62,A6&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E6="","впишите, что предъявляем",IF(F6="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F6)),ISNUMBER(SEARCH(" и ",F6)),LOWER(F6)="все"),"ответственный — один человек",IF(G6="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -2856,7 +2895,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I7" s="15" t="n"/>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J7" s="7">
         <f>IF(A7="","",IF(COUNTIF($A$3:$A$62,A7)&gt;1,"код повторяется",IF(C7="","нет названия",IF(D7="результат",IF(COUNTIF($A$3:$A$62,A7&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E7="","впишите, что предъявляем",IF(F7="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F7)),ISNUMBER(SEARCH(" и ",F7)),LOWER(F7)="все"),"ответственный — один человек",IF(G7="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -2936,7 +2979,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="J9" s="7">
         <f>IF(A9="","",IF(COUNTIF($A$3:$A$62,A9)&gt;1,"код повторяется",IF(C9="","нет названия",IF(D9="результат",IF(COUNTIF($A$3:$A$62,A9&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E9="","впишите, что предъявляем",IF(F9="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F9)),ISNUMBER(SEARCH(" и ",F9)),LOWER(F9)="все"),"ответственный — один человек",IF(G9="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -2983,7 +3030,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I10" s="15" t="n"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>1.3, 1.4, 2.1</t>
+        </is>
+      </c>
       <c r="J10" s="7">
         <f>IF(A10="","",IF(COUNTIF($A$3:$A$62,A10)&gt;1,"код повторяется",IF(C10="","нет названия",IF(D10="результат",IF(COUNTIF($A$3:$A$62,A10&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E10="","впишите, что предъявляем",IF(F10="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F10)),ISNUMBER(SEARCH(" и ",F10)),LOWER(F10)="все"),"ответственный — один человек",IF(G10="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -3063,7 +3114,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I12" s="15" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
       <c r="J12" s="7">
         <f>IF(A12="","",IF(COUNTIF($A$3:$A$62,A12)&gt;1,"код повторяется",IF(C12="","нет названия",IF(D12="результат",IF(COUNTIF($A$3:$A$62,A12&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E12="","впишите, что предъявляем",IF(F12="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F12)),ISNUMBER(SEARCH(" и ",F12)),LOWER(F12)="все"),"ответственный — один человек",IF(G12="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -3143,7 +3198,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>2.2, 3.1</t>
+        </is>
+      </c>
       <c r="J14" s="7">
         <f>IF(A14="","",IF(COUNTIF($A$3:$A$62,A14)&gt;1,"код повторяется",IF(C14="","нет названия",IF(D14="результат",IF(COUNTIF($A$3:$A$62,A14&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E14="","впишите, что предъявляем",IF(F14="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F14)),ISNUMBER(SEARCH(" и ",F14)),LOWER(F14)="все"),"ответственный — один человек",IF(G14="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -3190,7 +3249,11 @@
           <t>недель</t>
         </is>
       </c>
-      <c r="I15" s="15" t="n"/>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="J15" s="7">
         <f>IF(A15="","",IF(COUNTIF($A$3:$A$62,A15)&gt;1,"код повторяется",IF(C15="","нет названия",IF(D15="результат",IF(COUNTIF($A$3:$A$62,A15&amp;".*")=0,"разложите на пакеты работ","✓"),IF(E15="","впишите, что предъявляем",IF(F15="","нужен один ответственный",IF(OR(ISNUMBER(SEARCH(",",F15)),ISNUMBER(SEARCH(" и ",F15)),LOWER(F15)="все"),"ответственный — один человек",IF(G15="","оцените длительность","✓"))))))))</f>
         <v/>
@@ -4434,5 +4497,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>